--- a/VA_result_DTX.xlsx
+++ b/VA_result_DTX.xlsx
@@ -2144,10 +2144,10 @@
         <v>26</v>
       </c>
       <c r="B98" t="n">
-        <v>1016.76475017707</v>
+        <v>1016.76474851769</v>
       </c>
       <c r="C98" t="n">
-        <v>139.346256354778</v>
+        <v>139.346256127361</v>
       </c>
     </row>
     <row r="99">
@@ -2155,10 +2155,10 @@
         <v>101</v>
       </c>
       <c r="B99" t="n">
-        <v>1084.09082139861</v>
+        <v>1084.09081962535</v>
       </c>
       <c r="C99" t="n">
-        <v>148.573204848186</v>
+        <v>148.573204605163</v>
       </c>
     </row>
     <row r="100">
@@ -2166,10 +2166,10 @@
         <v>102</v>
       </c>
       <c r="B100" t="n">
-        <v>1054.50878922322</v>
+        <v>1054.50878754687</v>
       </c>
       <c r="C100" t="n">
-        <v>144.519026693122</v>
+        <v>144.51902646338</v>
       </c>
     </row>
     <row r="101">
@@ -2177,10 +2177,10 @@
         <v>103</v>
       </c>
       <c r="B101" t="n">
-        <v>1093.75350072407</v>
+        <v>1093.75349908692</v>
       </c>
       <c r="C101" t="n">
-        <v>149.897462194957</v>
+        <v>149.897461970588</v>
       </c>
     </row>
     <row r="102">
@@ -2188,10 +2188,10 @@
         <v>104</v>
       </c>
       <c r="B102" t="n">
-        <v>1113.79923164423</v>
+        <v>1113.79923008109</v>
       </c>
       <c r="C102" t="n">
-        <v>152.644702949647</v>
+        <v>152.644702735421</v>
       </c>
     </row>
     <row r="103">
@@ -2199,10 +2199,10 @@
         <v>105</v>
       </c>
       <c r="B103" t="n">
-        <v>1158.09215470873</v>
+        <v>1158.09215312996</v>
       </c>
       <c r="C103" t="n">
-        <v>158.714989130372</v>
+        <v>158.714988914004</v>
       </c>
     </row>
     <row r="104">
@@ -2210,10 +2210,10 @@
         <v>106</v>
       </c>
       <c r="B104" t="n">
-        <v>1109.41566181666</v>
+        <v>1109.41566025281</v>
       </c>
       <c r="C104" t="n">
-        <v>152.043940536478</v>
+        <v>152.043940322154</v>
       </c>
     </row>
     <row r="105">
@@ -2221,10 +2221,10 @@
         <v>107</v>
       </c>
       <c r="B105" t="n">
-        <v>1176.63987124769</v>
+        <v>1176.63986977992</v>
       </c>
       <c r="C105" t="n">
-        <v>161.256929007009</v>
+        <v>161.256928805853</v>
       </c>
     </row>
     <row r="106">
@@ -2232,10 +2232,10 @@
         <v>108</v>
       </c>
       <c r="B106" t="n">
-        <v>1142.382129184</v>
+        <v>1142.38212752448</v>
       </c>
       <c r="C106" t="n">
-        <v>156.561951032102</v>
+        <v>156.561950804667</v>
       </c>
     </row>
     <row r="107">
@@ -2243,10 +2243,10 @@
         <v>109</v>
       </c>
       <c r="B107" t="n">
-        <v>1218.44198850867</v>
+        <v>1218.44198703987</v>
       </c>
       <c r="C107" t="n">
-        <v>166.985853566015</v>
+        <v>166.985853364718</v>
       </c>
     </row>
     <row r="108">
@@ -2254,10 +2254,10 @@
         <v>110</v>
       </c>
       <c r="B108" t="n">
-        <v>1168.43112620794</v>
+        <v>1168.43112474403</v>
       </c>
       <c r="C108" t="n">
-        <v>160.131931419847</v>
+        <v>160.131931219221</v>
       </c>
     </row>
     <row r="109">
@@ -2265,10 +2265,10 @@
         <v>111</v>
       </c>
       <c r="B109" t="n">
-        <v>1247.44062696685</v>
+        <v>1247.44062559468</v>
       </c>
       <c r="C109" t="n">
-        <v>170.960078388255</v>
+        <v>170.960078200202</v>
       </c>
     </row>
     <row r="110">
@@ -2276,10 +2276,10 @@
         <v>112</v>
       </c>
       <c r="B110" t="n">
-        <v>1197.25067477944</v>
+        <v>1197.25067310812</v>
       </c>
       <c r="C110" t="n">
-        <v>164.081612211372</v>
+        <v>164.08161198232</v>
       </c>
     </row>
     <row r="111">
@@ -2287,10 +2287,10 @@
         <v>113</v>
       </c>
       <c r="B111" t="n">
-        <v>1265.32171227765</v>
+        <v>1265.32171083494</v>
       </c>
       <c r="C111" t="n">
-        <v>173.410657341929</v>
+        <v>173.410657144207</v>
       </c>
     </row>
     <row r="112">
@@ -2298,10 +2298,10 @@
         <v>114</v>
       </c>
       <c r="B112" t="n">
-        <v>1231.50286667736</v>
+        <v>1231.50286530054</v>
       </c>
       <c r="C112" t="n">
-        <v>168.775829543444</v>
+        <v>168.775829354752</v>
       </c>
     </row>
     <row r="113">
@@ -2309,10 +2309,10 @@
         <v>115</v>
       </c>
       <c r="B113" t="n">
-        <v>1306.02373220848</v>
+        <v>1306.02373085749</v>
       </c>
       <c r="C113" t="n">
-        <v>178.988815025357</v>
+        <v>178.988814840204</v>
       </c>
     </row>
     <row r="114">
@@ -2320,10 +2320,10 @@
         <v>116</v>
       </c>
       <c r="B114" t="n">
-        <v>1278.45148873961</v>
+        <v>1278.45148714126</v>
       </c>
       <c r="C114" t="n">
-        <v>175.21007573879</v>
+        <v>175.210075519738</v>
       </c>
     </row>
     <row r="115">
@@ -2331,10 +2331,10 @@
         <v>117</v>
       </c>
       <c r="B115" t="n">
-        <v>1345.77755996076</v>
+        <v>1345.77755824853</v>
       </c>
       <c r="C115" t="n">
-        <v>184.437024232145</v>
+        <v>184.437023997486</v>
       </c>
     </row>
     <row r="116">
@@ -2342,10 +2342,10 @@
         <v>118</v>
       </c>
       <c r="B116" t="n">
-        <v>1316.19552778551</v>
+        <v>1316.19552617019</v>
       </c>
       <c r="C116" t="n">
-        <v>180.382846077099</v>
+        <v>180.382845855722</v>
       </c>
     </row>
     <row r="117">
@@ -2353,10 +2353,10 @@
         <v>119</v>
       </c>
       <c r="B117" t="n">
-        <v>1355.44023928813</v>
+        <v>1355.44023771201</v>
       </c>
       <c r="C117" t="n">
-        <v>185.761281579177</v>
+        <v>185.761281363172</v>
       </c>
     </row>
     <row r="118">
@@ -2364,10 +2364,10 @@
         <v>120</v>
       </c>
       <c r="B118" t="n">
-        <v>1375.48597020791</v>
+        <v>1375.48596870579</v>
       </c>
       <c r="C118" t="n">
-        <v>188.508522333816</v>
+        <v>188.508522127953</v>
       </c>
     </row>
     <row r="119">
@@ -2375,10 +2375,10 @@
         <v>121</v>
       </c>
       <c r="B119" t="n">
-        <v>1419.77889327122</v>
+        <v>1419.77889175348</v>
       </c>
       <c r="C119" t="n">
-        <v>194.578808514379</v>
+        <v>194.578808306374</v>
       </c>
     </row>
     <row r="120">
@@ -2386,10 +2386,10 @@
         <v>122</v>
       </c>
       <c r="B120" t="n">
-        <v>1371.10240038054</v>
+        <v>1371.10239887772</v>
       </c>
       <c r="C120" t="n">
-        <v>187.907759920675</v>
+        <v>187.907759714715</v>
       </c>
     </row>
     <row r="121">
@@ -2397,10 +2397,10 @@
         <v>123</v>
       </c>
       <c r="B121" t="n">
-        <v>1438.3266098089</v>
+        <v>1438.32660840216</v>
       </c>
       <c r="C121" t="n">
-        <v>197.12074839084</v>
+        <v>197.120748198047</v>
       </c>
     </row>
     <row r="122">
@@ -2408,10 +2408,10 @@
         <v>124</v>
       </c>
       <c r="B122" t="n">
-        <v>1404.06886774675</v>
+        <v>1404.06886614827</v>
       </c>
       <c r="C122" t="n">
-        <v>192.425770416144</v>
+        <v>192.425770197074</v>
       </c>
     </row>
     <row r="123">
@@ -2419,10 +2419,10 @@
         <v>125</v>
       </c>
       <c r="B123" t="n">
-        <v>1480.12872707125</v>
+        <v>1480.12872566347</v>
       </c>
       <c r="C123" t="n">
-        <v>202.849672950033</v>
+        <v>202.849672757099</v>
       </c>
     </row>
     <row r="124">
@@ -2430,10 +2430,10 @@
         <v>126</v>
       </c>
       <c r="B124" t="n">
-        <v>1430.11786477103</v>
+        <v>1430.11786336815</v>
       </c>
       <c r="C124" t="n">
-        <v>195.995750803935</v>
+        <v>195.995750611673</v>
       </c>
     </row>
     <row r="125">
@@ -2441,10 +2441,10 @@
         <v>127</v>
       </c>
       <c r="B125" t="n">
-        <v>1509.12736552974</v>
+        <v>1509.12736421861</v>
       </c>
       <c r="C125" t="n">
-        <v>206.823897772317</v>
+        <v>206.823897592628</v>
       </c>
     </row>
     <row r="126">
@@ -2452,10 +2452,10 @@
         <v>128</v>
       </c>
       <c r="B126" t="n">
-        <v>1458.93741334225</v>
+        <v>1458.93741173196</v>
       </c>
       <c r="C126" t="n">
-        <v>199.945431595422</v>
+        <v>199.945431374733</v>
       </c>
     </row>
     <row r="127">
@@ -2463,10 +2463,10 @@
         <v>129</v>
       </c>
       <c r="B127" t="n">
-        <v>1527.00845084158</v>
+        <v>1527.0084494599</v>
       </c>
       <c r="C127" t="n">
-        <v>209.274476726132</v>
+        <v>209.274476536774</v>
       </c>
     </row>
     <row r="128">
@@ -2474,10 +2474,10 @@
         <v>130</v>
       </c>
       <c r="B128" t="n">
-        <v>1493.18960524099</v>
+        <v>1493.1896039252</v>
       </c>
       <c r="C128" t="n">
-        <v>204.639648927606</v>
+        <v>204.639648747278</v>
       </c>
     </row>
     <row r="129">
@@ -2485,10 +2485,10 @@
         <v>131</v>
       </c>
       <c r="B129" t="n">
-        <v>1567.71047077159</v>
+        <v>1567.71046948163</v>
       </c>
       <c r="C129" t="n">
-        <v>214.852634409448</v>
+        <v>214.85263423266</v>
       </c>
     </row>
     <row r="130">
@@ -2496,10 +2496,10 @@
         <v>132</v>
       </c>
       <c r="B130" t="n">
-        <v>1540.13822730286</v>
+        <v>1540.13822576553</v>
       </c>
       <c r="C130" t="n">
-        <v>211.073895122901</v>
+        <v>211.073894912212</v>
       </c>
     </row>
     <row r="131">
@@ -2507,10 +2507,10 @@
         <v>133</v>
       </c>
       <c r="B131" t="n">
-        <v>1607.464298525</v>
+        <v>1607.46429687379</v>
       </c>
       <c r="C131" t="n">
-        <v>220.30084361639</v>
+        <v>220.300843390095</v>
       </c>
     </row>
     <row r="132">
@@ -2518,10 +2518,10 @@
         <v>134</v>
       </c>
       <c r="B132" t="n">
-        <v>1577.88226634824</v>
+        <v>1577.88226479395</v>
       </c>
       <c r="C132" t="n">
-        <v>216.246665461139</v>
+        <v>216.246665248126</v>
       </c>
     </row>
     <row r="133">
@@ -2529,10 +2529,10 @@
         <v>135</v>
       </c>
       <c r="B133" t="n">
-        <v>1617.12697784925</v>
+        <v>1617.12697633417</v>
       </c>
       <c r="C133" t="n">
-        <v>221.625100962996</v>
+        <v>221.625100755356</v>
       </c>
     </row>
     <row r="134">
@@ -2540,10 +2540,10 @@
         <v>136</v>
       </c>
       <c r="B134" t="n">
-        <v>1637.17270877001</v>
+        <v>1637.17270732893</v>
       </c>
       <c r="C134" t="n">
-        <v>224.372341717769</v>
+        <v>224.372341520271</v>
       </c>
     </row>
     <row r="135">
@@ -2551,10 +2551,10 @@
         <v>137</v>
       </c>
       <c r="B135" t="n">
-        <v>1681.46563183508</v>
+        <v>1681.46563037837</v>
       </c>
       <c r="C135" t="n">
-        <v>230.442627898572</v>
+        <v>230.442627698932</v>
       </c>
     </row>
     <row r="136">
@@ -2562,10 +2562,10 @@
         <v>138</v>
       </c>
       <c r="B136" t="n">
-        <v>1632.78913894269</v>
+        <v>1632.78913750089</v>
       </c>
       <c r="C136" t="n">
-        <v>223.771579304634</v>
+        <v>223.771579107038</v>
       </c>
     </row>
     <row r="137">
@@ -2573,10 +2573,10 @@
         <v>139</v>
       </c>
       <c r="B137" t="n">
-        <v>1700.01334837297</v>
+        <v>1700.01334702726</v>
       </c>
       <c r="C137" t="n">
-        <v>232.984567775062</v>
+        <v>232.984567590634</v>
       </c>
     </row>
   </sheetData>
@@ -2635,7 +2635,7 @@
         <v>38.5897076142512</v>
       </c>
       <c r="D3" t="n">
-        <v>5.84481030904809</v>
+        <v>5.84481030904815</v>
       </c>
       <c r="E3" t="n">
         <v>1.35768668041547</v>
@@ -2709,13 +2709,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>880.419322745562</v>
+        <v>880.419322745563</v>
       </c>
       <c r="C7" t="n">
         <v>40.0086341332848</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.72127078081393</v>
+        <v>-1.72127078081387</v>
       </c>
       <c r="E7" t="n">
         <v>8.35399806344113</v>
@@ -2735,7 +2735,7 @@
         <v>42.4290714496252</v>
       </c>
       <c r="D8" t="n">
-        <v>2.59367632015344</v>
+        <v>2.59367632015342</v>
       </c>
       <c r="E8" t="n">
         <v>6.04978742407691</v>
@@ -2749,13 +2749,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>877.295317819317</v>
+        <v>877.295317819318</v>
       </c>
       <c r="C9" t="n">
         <v>40.2307810069611</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.87396641528357</v>
+        <v>-2.87396641528359</v>
       </c>
       <c r="E9" t="n">
         <v>-5.18109486622648</v>
@@ -2815,7 +2815,7 @@
         <v>47.5471772864491</v>
       </c>
       <c r="D12" t="n">
-        <v>5.15964666075108</v>
+        <v>5.1596466607511</v>
       </c>
       <c r="E12" t="n">
         <v>11.5348731635496</v>
@@ -2895,7 +2895,7 @@
         <v>64.9378275403955</v>
       </c>
       <c r="D16" t="n">
-        <v>18.5210388066037</v>
+        <v>18.5210388066036</v>
       </c>
       <c r="E16" t="n">
         <v>6.69275204554327</v>
@@ -2909,13 +2909,13 @@
         <v>17</v>
       </c>
       <c r="B17" t="n">
-        <v>1135.26047112508</v>
+        <v>1135.26047112509</v>
       </c>
       <c r="C17" t="n">
         <v>49.0443949187084</v>
       </c>
       <c r="D17" t="n">
-        <v>-24.3754932366013</v>
+        <v>-24.3754932366012</v>
       </c>
       <c r="E17" t="n">
         <v>-24.4748449766053</v>
@@ -2975,7 +2975,7 @@
         <v>87.7549051100208</v>
       </c>
       <c r="D20" t="n">
-        <v>8.23217102785348</v>
+        <v>8.23217102785343</v>
       </c>
       <c r="E20" t="n">
         <v>9.03593370811444</v>
@@ -3015,7 +3015,7 @@
         <v>108.743157655878</v>
       </c>
       <c r="D22" t="n">
-        <v>4.99999999999998</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>8.74315765587814</v>
@@ -3055,7 +3055,7 @@
         <v>124.314776503352</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.41626585045911</v>
+        <v>-4.41626585045913</v>
       </c>
       <c r="E24" t="n">
         <v>-10.8619641000738</v>
@@ -3092,13 +3092,13 @@
         <v>2521.14623605159</v>
       </c>
       <c r="C26" t="n">
-        <v>145.583987522761</v>
+        <v>145.583987291623</v>
       </c>
       <c r="D26" t="n">
         <v>6.96389093588798</v>
       </c>
       <c r="E26" t="n">
-        <v>7.84366688817044</v>
+        <v>7.84366671695156</v>
       </c>
       <c r="F26" t="s">
         <v>145</v>
@@ -3109,16 +3109,16 @@
         <v>104</v>
       </c>
       <c r="B27" t="n">
-        <v>2678.35091620166</v>
+        <v>2678.35091446645</v>
       </c>
       <c r="C27" t="n">
-        <v>156.165140405877</v>
+        <v>156.165140194358</v>
       </c>
       <c r="D27" t="n">
-        <v>6.23544473153097</v>
+        <v>6.23544466270487</v>
       </c>
       <c r="E27" t="n">
-        <v>7.26807464417187</v>
+        <v>7.268074669187</v>
       </c>
       <c r="F27" t="s">
         <v>145</v>
@@ -3129,16 +3129,16 @@
         <v>108</v>
       </c>
       <c r="B28" t="n">
-        <v>2788.81614003086</v>
+        <v>2788.81613779028</v>
       </c>
       <c r="C28" t="n">
-        <v>163.659953601555</v>
+        <v>163.659953397202</v>
       </c>
       <c r="D28" t="n">
-        <v>4.12437456051731</v>
+        <v>4.12437454432022</v>
       </c>
       <c r="E28" t="n">
-        <v>4.79928694470417</v>
+        <v>4.79928695579326</v>
       </c>
       <c r="F28" t="s">
         <v>145</v>
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="B29" t="n">
-        <v>2901.1288343181</v>
+        <v>2901.12883196448</v>
       </c>
       <c r="C29" t="n">
-        <v>171.314228530525</v>
+        <v>171.314228330371</v>
       </c>
       <c r="D29" t="n">
-        <v>4.02725345264208</v>
+        <v>4.02725345182469</v>
       </c>
       <c r="E29" t="n">
-        <v>4.67693822497677</v>
+        <v>4.67693823338198</v>
       </c>
       <c r="F29" t="s">
         <v>145</v>
@@ -3169,16 +3169,16 @@
         <v>116</v>
       </c>
       <c r="B30" t="n">
-        <v>3049.59386430702</v>
+        <v>3049.59386158691</v>
       </c>
       <c r="C30" t="n">
-        <v>181.447806906803</v>
+        <v>181.447806684029</v>
       </c>
       <c r="D30" t="n">
-        <v>5.11749179259822</v>
+        <v>5.11749178411689</v>
       </c>
       <c r="E30" t="n">
-        <v>5.91519949230133</v>
+        <v>5.91519948600912</v>
       </c>
       <c r="F30" t="s">
         <v>145</v>
@@ -3189,16 +3189,16 @@
         <v>120</v>
       </c>
       <c r="B31" t="n">
-        <v>3204.56441835413</v>
+        <v>3204.56441592794</v>
       </c>
       <c r="C31" t="n">
-        <v>192.028959789927</v>
+        <v>192.028959586772</v>
       </c>
       <c r="D31" t="n">
-        <v>5.08167844449401</v>
+        <v>5.08167845866496</v>
       </c>
       <c r="E31" t="n">
-        <v>5.83151323981514</v>
+        <v>5.83151325778699</v>
       </c>
       <c r="F31" t="s">
         <v>145</v>
@@ -3209,16 +3209,16 @@
         <v>124</v>
       </c>
       <c r="B32" t="n">
-        <v>3314.32391913856</v>
+        <v>3314.32391682927</v>
       </c>
       <c r="C32" t="n">
-        <v>199.523772985607</v>
+        <v>199.523772789618</v>
       </c>
       <c r="D32" t="n">
-        <v>3.42509890441864</v>
+        <v>3.42509891065956</v>
       </c>
       <c r="E32" t="n">
-        <v>3.90295984724336</v>
+        <v>3.90295985510427</v>
       </c>
       <c r="F32" t="s">
         <v>145</v>
@@ -3229,16 +3229,16 @@
         <v>128</v>
       </c>
       <c r="B33" t="n">
-        <v>3426.41368732828</v>
+        <v>3426.41368509661</v>
       </c>
       <c r="C33" t="n">
-        <v>207.178047914652</v>
+        <v>207.178047722861</v>
       </c>
       <c r="D33" t="n">
-        <v>3.38197988260749</v>
+        <v>3.38197988730611</v>
       </c>
       <c r="E33" t="n">
-        <v>3.83627214667632</v>
+        <v>3.83627215254878</v>
       </c>
       <c r="F33" t="s">
         <v>145</v>
@@ -3249,16 +3249,16 @@
         <v>132</v>
       </c>
       <c r="B34" t="n">
-        <v>3574.80829869256</v>
+        <v>3574.80829615276</v>
       </c>
       <c r="C34" t="n">
-        <v>217.311626290856</v>
+        <v>217.311626076447</v>
       </c>
       <c r="D34" t="n">
-        <v>4.33090177969715</v>
+        <v>4.33090177352489</v>
       </c>
       <c r="E34" t="n">
-        <v>4.89124136374683</v>
+        <v>4.89124135735719</v>
       </c>
       <c r="F34" t="s">
         <v>145</v>
@@ -3269,16 +3269,16 @@
         <v>136</v>
       </c>
       <c r="B35" t="n">
-        <v>3729.75660867545</v>
+        <v>3729.75660644742</v>
       </c>
       <c r="C35" t="n">
-        <v>227.892779174009</v>
+        <v>227.892778979219</v>
       </c>
       <c r="D35" t="n">
-        <v>4.33445088620708</v>
+        <v>4.33445089800815</v>
       </c>
       <c r="E35" t="n">
-        <v>4.86911494969477</v>
+        <v>4.86911496352678</v>
       </c>
       <c r="F35" t="s">
         <v>145</v>
@@ -3323,16 +3323,16 @@
         <v>1045.85704501517</v>
       </c>
       <c r="C2" t="n">
-        <v>962.160673534252</v>
+        <v>962.16067435703</v>
       </c>
       <c r="D2" t="n">
-        <v>83.6963714809143</v>
+        <v>83.6963706581361</v>
       </c>
       <c r="E2" t="n">
         <v>38.5897076142512</v>
       </c>
       <c r="F2" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
     </row>
     <row r="3">
@@ -3343,16 +3343,16 @@
         <v>1067.27857683758</v>
       </c>
       <c r="C3" t="n">
-        <v>995.103382844431</v>
+        <v>995.103383290184</v>
       </c>
       <c r="D3" t="n">
-        <v>72.1751939931466</v>
+        <v>72.1751935473938</v>
       </c>
       <c r="E3" t="n">
         <v>39.2448890813324</v>
       </c>
       <c r="F3" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
     </row>
     <row r="4">
@@ -3363,16 +3363,16 @@
         <v>1038.86976713801</v>
       </c>
       <c r="C4" t="n">
-        <v>1000.00897206187</v>
+        <v>1000.00897248104</v>
       </c>
       <c r="D4" t="n">
-        <v>38.8607950761375</v>
+        <v>38.8607946569727</v>
       </c>
       <c r="E4" t="n">
         <v>39.324757142135</v>
       </c>
       <c r="F4" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
     </row>
     <row r="5">
@@ -3383,16 +3383,16 @@
         <v>895.839140107324</v>
       </c>
       <c r="C5" t="n">
-        <v>955.509534975268</v>
+        <v>955.509535454537</v>
       </c>
       <c r="D5" t="n">
-        <v>-59.6703948679447</v>
+        <v>-59.670395347213</v>
       </c>
       <c r="E5" t="n">
         <v>36.9240035885522</v>
       </c>
       <c r="F5" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
     </row>
     <row r="6">
@@ -3403,16 +3403,16 @@
         <v>880.419322745562</v>
       </c>
       <c r="C6" t="n">
-        <v>966.604389418169</v>
+        <v>966.604390146194</v>
       </c>
       <c r="D6" t="n">
-        <v>-86.1850666726074</v>
+        <v>-86.1850674006323</v>
       </c>
       <c r="E6" t="n">
         <v>40.0086341332848</v>
       </c>
       <c r="F6" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
     </row>
     <row r="7">
@@ -3423,16 +3423,16 @@
         <v>903.254550237668</v>
       </c>
       <c r="C7" t="n">
-        <v>982.909202194412</v>
+        <v>982.909203060497</v>
       </c>
       <c r="D7" t="n">
-        <v>-79.6546519567432</v>
+        <v>-79.6546528228291</v>
       </c>
       <c r="E7" t="n">
         <v>42.4290714496252</v>
       </c>
       <c r="F7" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
     </row>
     <row r="8">
@@ -3443,16 +3443,16 @@
         <v>877.295317819317</v>
       </c>
       <c r="C8" t="n">
-        <v>946.734900854286</v>
+        <v>946.734901741502</v>
       </c>
       <c r="D8" t="n">
-        <v>-69.4395830349686</v>
+        <v>-69.439583922185</v>
       </c>
       <c r="E8" t="n">
         <v>40.2307810069611</v>
       </c>
       <c r="F8" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
     </row>
     <row r="9">
@@ -3463,16 +3463,16 @@
         <v>983.824617972529</v>
       </c>
       <c r="C9" t="n">
-        <v>984.404985478263</v>
+        <v>984.40498635892</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.580367505733228</v>
+        <v>-0.580368386390234</v>
       </c>
       <c r="E9" t="n">
         <v>42.6687771131109</v>
       </c>
       <c r="F9" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
     </row>
     <row r="10">
@@ -3483,16 +3483,16 @@
         <v>1037.6039560867</v>
       </c>
       <c r="C10" t="n">
-        <v>1006.20866737862</v>
+        <v>1006.20866809994</v>
       </c>
       <c r="D10" t="n">
-        <v>31.3952887080824</v>
+        <v>31.395287986761</v>
       </c>
       <c r="E10" t="n">
         <v>42.6298752469356</v>
       </c>
       <c r="F10" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
     </row>
     <row r="11">
@@ -3503,16 +3503,16 @@
         <v>1091.14065395875</v>
       </c>
       <c r="C11" t="n">
-        <v>1095.38452688579</v>
+        <v>1095.38452749777</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.24387292704407</v>
+        <v>-4.2438735390269</v>
       </c>
       <c r="E11" t="n">
         <v>47.5471772864491</v>
       </c>
       <c r="F11" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
     </row>
     <row r="12">
@@ -3523,16 +3523,16 @@
         <v>1143.08791762752</v>
       </c>
       <c r="C12" t="n">
-        <v>1163.12471517862</v>
+        <v>1163.12471583975</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.0367975511031</v>
+        <v>-20.036798212231</v>
       </c>
       <c r="E12" t="n">
         <v>52.571490172106</v>
       </c>
       <c r="F12" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
     </row>
     <row r="13">
@@ -3543,16 +3543,16 @@
         <v>1114.90897830289</v>
       </c>
       <c r="C13" t="n">
-        <v>1205.22372509801</v>
+        <v>1205.22372581131</v>
       </c>
       <c r="D13" t="n">
-        <v>-90.3147467951284</v>
+        <v>-90.3147475084205</v>
       </c>
       <c r="E13" t="n">
         <v>55.9128976329543</v>
       </c>
       <c r="F13" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
     </row>
     <row r="14">
@@ -3563,16 +3563,16 @@
         <v>1266.59424936741</v>
       </c>
       <c r="C14" t="n">
-        <v>1253.37367998259</v>
+        <v>1253.37368087637</v>
       </c>
       <c r="D14" t="n">
-        <v>13.2205693848164</v>
+        <v>13.220568491035</v>
       </c>
       <c r="E14" t="n">
         <v>60.8643289214959</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
     </row>
     <row r="15">
@@ -3583,16 +3583,16 @@
         <v>1501.18066181495</v>
       </c>
       <c r="C15" t="n">
-        <v>1338.03601236871</v>
+        <v>1338.03601309232</v>
       </c>
       <c r="D15" t="n">
-        <v>163.144649446244</v>
+        <v>163.144648722632</v>
       </c>
       <c r="E15" t="n">
         <v>64.9378275403955</v>
       </c>
       <c r="F15" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
     </row>
     <row r="16">
@@ -3603,16 +3603,16 @@
         <v>1135.26047112508</v>
       </c>
       <c r="C16" t="n">
-        <v>1160.55517372143</v>
+        <v>1160.55517401615</v>
       </c>
       <c r="D16" t="n">
-        <v>-25.2947025963441</v>
+        <v>-25.2947028910637</v>
       </c>
       <c r="E16" t="n">
         <v>49.0443949187084</v>
       </c>
       <c r="F16" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
     </row>
     <row r="17">
@@ -3623,16 +3623,16 @@
         <v>1332.87034060975</v>
       </c>
       <c r="C17" t="n">
-        <v>1496.31261224082</v>
+        <v>1496.31261290338</v>
       </c>
       <c r="D17" t="n">
-        <v>-163.442271631066</v>
+        <v>-163.442272293625</v>
       </c>
       <c r="E17" t="n">
         <v>74.8455798988774</v>
       </c>
       <c r="F17" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
     </row>
     <row r="18">
@@ -3643,16 +3643,16 @@
         <v>1543.75677367368</v>
       </c>
       <c r="C18" t="n">
-        <v>1521.93161805811</v>
+        <v>1521.93161911544</v>
       </c>
       <c r="D18" t="n">
-        <v>21.8251556155771</v>
+        <v>21.8251545582457</v>
       </c>
       <c r="E18" t="n">
         <v>80.4825548107267</v>
       </c>
       <c r="F18" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
     </row>
     <row r="19">
@@ -3663,16 +3663,16 @@
         <v>1670.84147153657</v>
       </c>
       <c r="C19" t="n">
-        <v>1668.96677449178</v>
+        <v>1668.9667752766</v>
       </c>
       <c r="D19" t="n">
-        <v>1.87469704478837</v>
+        <v>1.87469625996916</v>
       </c>
       <c r="E19" t="n">
         <v>87.7549051100208</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
     </row>
     <row r="20">
@@ -3683,16 +3683,16 @@
         <v>2000</v>
       </c>
       <c r="C20" t="n">
-        <v>1854.78530581306</v>
+        <v>1854.78530657527</v>
       </c>
       <c r="D20" t="n">
-        <v>145.214694186941</v>
+        <v>145.214693424727</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
     </row>
     <row r="21">
@@ -3703,16 +3703,16 @@
         <v>2100</v>
       </c>
       <c r="C21" t="n">
-        <v>2030.15147954547</v>
+        <v>2030.15147998593</v>
       </c>
       <c r="D21" t="n">
-        <v>69.8485204545341</v>
+        <v>69.8485200140728</v>
       </c>
       <c r="E21" t="n">
         <v>108.743157655878</v>
       </c>
       <c r="F21" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
     </row>
     <row r="22">
@@ -3723,16 +3723,16 @@
         <v>2356.44230769231</v>
       </c>
       <c r="C22" t="n">
-        <v>2471.15423836994</v>
+        <v>2471.15423893783</v>
       </c>
       <c r="D22" t="n">
-        <v>-114.711930677636</v>
+        <v>-114.711931245524</v>
       </c>
       <c r="E22" t="n">
         <v>139.46322156225</v>
       </c>
       <c r="F22" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
     </row>
     <row r="23">
@@ -3743,16 +3743,16 @@
         <v>2252.37555077192</v>
       </c>
       <c r="C23" t="n">
-        <v>2188.22689877903</v>
+        <v>2188.22689971901</v>
       </c>
       <c r="D23" t="n">
-        <v>64.1486519928898</v>
+        <v>64.1486510529115</v>
       </c>
       <c r="E23" t="n">
         <v>124.314776503352</v>
       </c>
       <c r="F23" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
     </row>
     <row r="24">
@@ -3763,16 +3763,16 @@
         <v>2357.00684968791</v>
       </c>
       <c r="C24" t="n">
-        <v>2381.83123323787</v>
+        <v>2381.83123395207</v>
       </c>
       <c r="D24" t="n">
-        <v>-24.8243835499536</v>
+        <v>-24.8243842641575</v>
       </c>
       <c r="E24" t="n">
         <v>134.995398175514</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
     </row>
     <row r="25">
@@ -3783,16 +3783,16 @@
         <v>2521.14623605159</v>
       </c>
       <c r="C25" t="n">
-        <v>2520.53384944466</v>
+        <v>2520.53384690603</v>
       </c>
       <c r="D25" t="n">
-        <v>0.612386606928223</v>
+        <v>0.612389145557622</v>
       </c>
       <c r="E25" t="n">
-        <v>145.583987522761</v>
+        <v>145.583987291623</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.29855088747308</v>
+        <v>-3.29854793544064</v>
       </c>
     </row>
   </sheetData>
@@ -3849,31 +3849,31 @@
         <v>9.23693404109287</v>
       </c>
       <c r="C2" t="n">
-        <v>14.2986279212355</v>
+        <v>14.2986295661159</v>
       </c>
       <c r="D2" t="n">
-        <v>234.529000775003</v>
+        <v>234.529000979742</v>
       </c>
       <c r="E2" t="n">
-        <v>962.160673534252</v>
+        <v>962.16067435703</v>
       </c>
       <c r="F2" t="n">
         <v>1045.85704501517</v>
       </c>
       <c r="G2" t="n">
-        <v>83.6963714809143</v>
+        <v>83.6963706581362</v>
       </c>
       <c r="H2" t="n">
-        <v>21.4537950382202</v>
+        <v>21.4537948334267</v>
       </c>
       <c r="I2" t="n">
-        <v>255.982795813224</v>
+        <v>255.982795813169</v>
       </c>
       <c r="J2" t="n">
         <v>1045.85704501517</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="3">
@@ -3884,31 +3884,31 @@
         <v>9.61533075382236</v>
       </c>
       <c r="C3" t="n">
-        <v>14.2986279212355</v>
+        <v>14.2986295661159</v>
       </c>
       <c r="D3" t="n">
-        <v>240.070159393593</v>
+        <v>240.070159599213</v>
       </c>
       <c r="E3" t="n">
-        <v>962.160673534252</v>
+        <v>962.16067435703</v>
       </c>
       <c r="F3" t="n">
         <v>1045.85704501517</v>
       </c>
       <c r="G3" t="n">
-        <v>83.6963714809143</v>
+        <v>83.6963706581362</v>
       </c>
       <c r="H3" t="n">
-        <v>21.2419141710235</v>
+        <v>21.2419139658697</v>
       </c>
       <c r="I3" t="n">
-        <v>261.312073564617</v>
+        <v>261.312073565083</v>
       </c>
       <c r="J3" t="n">
         <v>1045.85704501517</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="4">
@@ -3919,31 +3919,31 @@
         <v>8.96665067485753</v>
       </c>
       <c r="C4" t="n">
-        <v>14.2986279212355</v>
+        <v>14.2986295661159</v>
       </c>
       <c r="D4" t="n">
-        <v>230.571030333154</v>
+        <v>230.571030537263</v>
       </c>
       <c r="E4" t="n">
-        <v>962.160673534252</v>
+        <v>962.16067435703</v>
       </c>
       <c r="F4" t="n">
         <v>1045.85704501517</v>
       </c>
       <c r="G4" t="n">
-        <v>83.6963714809143</v>
+        <v>83.6963706581362</v>
       </c>
       <c r="H4" t="n">
-        <v>20.8181524366301</v>
+        <v>20.8181522307555</v>
       </c>
       <c r="I4" t="n">
-        <v>251.389182769784</v>
+        <v>251.389182768018</v>
       </c>
       <c r="J4" t="n">
         <v>1045.85704501517</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="5">
@@ -3954,31 +3954,31 @@
         <v>10.7707921444785</v>
       </c>
       <c r="C5" t="n">
-        <v>14.2986279212355</v>
+        <v>14.2986295661159</v>
       </c>
       <c r="D5" t="n">
-        <v>256.990483032501</v>
+        <v>256.990483240812</v>
       </c>
       <c r="E5" t="n">
-        <v>962.160673534252</v>
+        <v>962.16067435703</v>
       </c>
       <c r="F5" t="n">
         <v>1045.85704501517</v>
       </c>
       <c r="G5" t="n">
-        <v>83.6963714809143</v>
+        <v>83.6963706581362</v>
       </c>
       <c r="H5" t="n">
-        <v>20.1825098350401</v>
+        <v>20.1825096280844</v>
       </c>
       <c r="I5" t="n">
-        <v>277.172992867541</v>
+        <v>277.172992868896</v>
       </c>
       <c r="J5" t="n">
         <v>1045.85704501517</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="6">
@@ -3989,31 +3989,31 @@
         <v>9.39376000248317</v>
       </c>
       <c r="C6" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
       <c r="D6" t="n">
-        <v>242.662609517839</v>
+        <v>242.662609733194</v>
       </c>
       <c r="E6" t="n">
-        <v>995.10334229187</v>
+        <v>995.103343157178</v>
       </c>
       <c r="F6" t="n">
         <v>1067.27857683758</v>
       </c>
       <c r="G6" t="n">
-        <v>72.1752345457077</v>
+        <v>72.1752336803995</v>
       </c>
       <c r="H6" t="n">
-        <v>19.3349863662533</v>
+        <v>19.3349861578562</v>
       </c>
       <c r="I6" t="n">
-        <v>261.997595884093</v>
+        <v>261.99759589105</v>
       </c>
       <c r="J6" t="n">
         <v>1067.27857683758</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="7">
@@ -4024,31 +4024,31 @@
         <v>9.77858118766171</v>
       </c>
       <c r="C7" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
       <c r="D7" t="n">
-        <v>248.29784670446</v>
+        <v>248.297846920711</v>
       </c>
       <c r="E7" t="n">
-        <v>995.10334229187</v>
+        <v>995.103343157178</v>
       </c>
       <c r="F7" t="n">
         <v>1067.27857683758</v>
       </c>
       <c r="G7" t="n">
-        <v>72.1752345457077</v>
+        <v>72.1752336803995</v>
       </c>
       <c r="H7" t="n">
-        <v>18.479505886808</v>
+        <v>18.4795056746624</v>
       </c>
       <c r="I7" t="n">
-        <v>266.777352591268</v>
+        <v>266.777352595373</v>
       </c>
       <c r="J7" t="n">
         <v>1067.27857683758</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="8">
@@ -4059,31 +4059,31 @@
         <v>9.11888772735565</v>
       </c>
       <c r="C8" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
       <c r="D8" t="n">
-        <v>238.637440098825</v>
+        <v>238.63744031354</v>
       </c>
       <c r="E8" t="n">
-        <v>995.10334229187</v>
+        <v>995.103343157178</v>
       </c>
       <c r="F8" t="n">
         <v>1067.27857683758</v>
       </c>
       <c r="G8" t="n">
-        <v>72.1752345457077</v>
+        <v>72.1752336803995</v>
       </c>
       <c r="H8" t="n">
-        <v>17.6160683967042</v>
+        <v>17.6160681785031</v>
       </c>
       <c r="I8" t="n">
-        <v>256.253508495529</v>
+        <v>256.253508492043</v>
       </c>
       <c r="J8" t="n">
         <v>1067.27857683758</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="9">
@@ -4094,31 +4094,31 @@
         <v>10.9536601638319</v>
       </c>
       <c r="C9" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
       <c r="D9" t="n">
-        <v>265.505445970746</v>
+        <v>265.505446189734</v>
       </c>
       <c r="E9" t="n">
-        <v>995.10334229187</v>
+        <v>995.103343157178</v>
       </c>
       <c r="F9" t="n">
         <v>1067.27857683758</v>
       </c>
       <c r="G9" t="n">
-        <v>72.1752345457077</v>
+        <v>72.1752336803995</v>
       </c>
       <c r="H9" t="n">
-        <v>16.7446738959418</v>
+        <v>16.7446736693781</v>
       </c>
       <c r="I9" t="n">
-        <v>282.250119866688</v>
+        <v>282.250119859112</v>
       </c>
       <c r="J9" t="n">
         <v>1067.27857683758</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="10">
@@ -4129,31 +4129,31 @@
         <v>9.99617052517854</v>
       </c>
       <c r="C10" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
       <c r="D10" t="n">
-        <v>252.418180790802</v>
+        <v>252.418181032184</v>
       </c>
       <c r="E10" t="n">
-        <v>1000.00892654754</v>
+        <v>1000.00892751154</v>
       </c>
       <c r="F10" t="n">
         <v>1038.86976713801</v>
       </c>
       <c r="G10" t="n">
-        <v>38.8608405904653</v>
+        <v>38.8608396264748</v>
       </c>
       <c r="H10" t="n">
-        <v>15.8653223845209</v>
+        <v>15.8653221472877</v>
       </c>
       <c r="I10" t="n">
-        <v>268.283503175323</v>
+        <v>268.283503179471</v>
       </c>
       <c r="J10" t="n">
         <v>1038.86976713801</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="11">
@@ -4164,31 +4164,31 @@
         <v>10.3276944445079</v>
       </c>
       <c r="C11" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
       <c r="D11" t="n">
-        <v>257.272944484729</v>
+        <v>257.272944726883</v>
       </c>
       <c r="E11" t="n">
-        <v>1000.00892654754</v>
+        <v>1000.00892751154</v>
       </c>
       <c r="F11" t="n">
         <v>1038.86976713801</v>
       </c>
       <c r="G11" t="n">
-        <v>38.8608405904653</v>
+        <v>38.8608396264748</v>
       </c>
       <c r="H11" t="n">
-        <v>13.0535368851907</v>
+        <v>13.0535366421839</v>
       </c>
       <c r="I11" t="n">
-        <v>270.32648136992</v>
+        <v>270.326481369067</v>
       </c>
       <c r="J11" t="n">
         <v>1038.86976713801</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="12">
@@ -4199,31 +4199,31 @@
         <v>8.43179753569241</v>
       </c>
       <c r="C12" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
       <c r="D12" t="n">
-        <v>229.50984522189</v>
+        <v>229.509845459629</v>
       </c>
       <c r="E12" t="n">
-        <v>1000.00892654754</v>
+        <v>1000.00892751154</v>
       </c>
       <c r="F12" t="n">
         <v>1038.86976713801</v>
       </c>
       <c r="G12" t="n">
-        <v>38.8608405904653</v>
+        <v>38.8608396264748</v>
       </c>
       <c r="H12" t="n">
-        <v>8.3093173979512</v>
+        <v>8.30931715406697</v>
       </c>
       <c r="I12" t="n">
-        <v>237.819162619841</v>
+        <v>237.819162613695</v>
       </c>
       <c r="J12" t="n">
         <v>1038.86976713801</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="13">
@@ -4234,31 +4234,31 @@
         <v>10.5690946367562</v>
       </c>
       <c r="C13" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
       <c r="D13" t="n">
-        <v>260.807956050124</v>
+        <v>260.80795629284</v>
       </c>
       <c r="E13" t="n">
-        <v>1000.00892654754</v>
+        <v>1000.00892751154</v>
       </c>
       <c r="F13" t="n">
         <v>1038.86976713801</v>
       </c>
       <c r="G13" t="n">
-        <v>38.8608405904653</v>
+        <v>38.8608396264748</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6326639228024</v>
+        <v>1.63266368293675</v>
       </c>
       <c r="I13" t="n">
-        <v>262.440619972926</v>
+        <v>262.440619975776</v>
       </c>
       <c r="J13" t="n">
         <v>1038.86976713801</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="14">
@@ -4269,31 +4269,31 @@
         <v>9.78700271451556</v>
       </c>
       <c r="C14" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
       <c r="D14" t="n">
-        <v>247.019344355291</v>
+        <v>247.019344534288</v>
       </c>
       <c r="E14" t="n">
-        <v>955.509501869714</v>
+        <v>955.509502580523</v>
       </c>
       <c r="F14" t="n">
         <v>895.839140107324</v>
       </c>
       <c r="G14" t="n">
-        <v>-59.6703617623903</v>
+        <v>-59.6703624731987</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.97642354025568</v>
+        <v>-6.97642377120672</v>
       </c>
       <c r="I14" t="n">
-        <v>240.042920815036</v>
+        <v>240.042920763081</v>
       </c>
       <c r="J14" t="n">
         <v>895.839140107324</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="15">
@@ -4304,31 +4304,31 @@
         <v>9.43061325992536</v>
       </c>
       <c r="C15" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
       <c r="D15" t="n">
-        <v>241.800455206831</v>
+        <v>241.800455384998</v>
       </c>
       <c r="E15" t="n">
-        <v>955.509501869714</v>
+        <v>955.509502580523</v>
       </c>
       <c r="F15" t="n">
         <v>895.839140107324</v>
       </c>
       <c r="G15" t="n">
-        <v>-59.6703617623903</v>
+        <v>-59.6703624731987</v>
       </c>
       <c r="H15" t="n">
-        <v>-13.5965252856157</v>
+        <v>-13.5965254917012</v>
       </c>
       <c r="I15" t="n">
-        <v>228.203929921215</v>
+        <v>228.203929893296</v>
       </c>
       <c r="J15" t="n">
         <v>895.839140107324</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="16">
@@ -4339,31 +4339,31 @@
         <v>8.33745714440349</v>
       </c>
       <c r="C16" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
       <c r="D16" t="n">
-        <v>225.792516376457</v>
+        <v>225.792516552078</v>
       </c>
       <c r="E16" t="n">
-        <v>955.509501869714</v>
+        <v>955.509502580523</v>
       </c>
       <c r="F16" t="n">
         <v>895.839140107324</v>
       </c>
       <c r="G16" t="n">
-        <v>-59.6703617623903</v>
+        <v>-59.6703624731987</v>
       </c>
       <c r="H16" t="n">
-        <v>-18.2276413132776</v>
+        <v>-18.2276414785468</v>
       </c>
       <c r="I16" t="n">
-        <v>207.564875063179</v>
+        <v>207.564875073531</v>
       </c>
       <c r="J16" t="n">
         <v>895.839140107324</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="17">
@@ -4374,31 +4374,31 @@
         <v>9.36893046970783</v>
       </c>
       <c r="C17" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
       <c r="D17" t="n">
-        <v>240.897185931136</v>
+        <v>240.897186109159</v>
       </c>
       <c r="E17" t="n">
-        <v>955.509501869714</v>
+        <v>955.509502580523</v>
       </c>
       <c r="F17" t="n">
         <v>895.839140107324</v>
       </c>
       <c r="G17" t="n">
-        <v>-59.6703617623903</v>
+        <v>-59.6703624731987</v>
       </c>
       <c r="H17" t="n">
-        <v>-20.8697716232414</v>
+        <v>-20.8697717317434</v>
       </c>
       <c r="I17" t="n">
-        <v>220.027414307894</v>
+        <v>220.027414377415</v>
       </c>
       <c r="J17" t="n">
         <v>895.839140107324</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="18">
@@ -4409,31 +4409,31 @@
         <v>9.74751579800055</v>
       </c>
       <c r="C18" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
       <c r="D18" t="n">
-        <v>237.922167925132</v>
+        <v>237.922167878786</v>
       </c>
       <c r="E18" t="n">
-        <v>966.60440156832</v>
+        <v>966.604401385309</v>
       </c>
       <c r="F18" t="n">
         <v>880.419322745562</v>
       </c>
       <c r="G18" t="n">
-        <v>-86.1850788227581</v>
+        <v>-86.1850786397468</v>
       </c>
       <c r="H18" t="n">
-        <v>-21.5229162155071</v>
+        <v>-21.5229162512911</v>
       </c>
       <c r="I18" t="n">
-        <v>216.399251709625</v>
+        <v>216.399251627495</v>
       </c>
       <c r="J18" t="n">
-        <v>880.419322745562</v>
+        <v>880.419322745563</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.000000000000113686837721616</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="19">
@@ -4444,31 +4444,31 @@
         <v>9.67083034417807</v>
       </c>
       <c r="C19" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
       <c r="D19" t="n">
-        <v>236.799202928148</v>
+        <v>236.799202881624</v>
       </c>
       <c r="E19" t="n">
-        <v>966.60440156832</v>
+        <v>966.604401385309</v>
       </c>
       <c r="F19" t="n">
         <v>880.419322745562</v>
       </c>
       <c r="G19" t="n">
-        <v>-86.1850788227581</v>
+        <v>-86.1850786397468</v>
       </c>
       <c r="H19" t="n">
-        <v>-21.7935154484864</v>
+        <v>-21.7935154225683</v>
       </c>
       <c r="I19" t="n">
-        <v>215.005687479662</v>
+        <v>215.005687459056</v>
       </c>
       <c r="J19" t="n">
-        <v>880.419322745562</v>
+        <v>880.419322745563</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000000000000113686837721616</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="20">
@@ -4479,31 +4479,31 @@
         <v>8.76118531638173</v>
       </c>
       <c r="C20" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
       <c r="D20" t="n">
-        <v>223.478560290234</v>
+        <v>223.478560241591</v>
       </c>
       <c r="E20" t="n">
-        <v>966.60440156832</v>
+        <v>966.604401385309</v>
       </c>
       <c r="F20" t="n">
         <v>880.419322745562</v>
       </c>
       <c r="G20" t="n">
-        <v>-86.1850788227581</v>
+        <v>-86.1850786397468</v>
       </c>
       <c r="H20" t="n">
-        <v>-21.6815693221792</v>
+        <v>-21.6815692455751</v>
       </c>
       <c r="I20" t="n">
-        <v>201.796990968055</v>
+        <v>201.796990996016</v>
       </c>
       <c r="J20" t="n">
-        <v>880.419322745562</v>
+        <v>880.419322745563</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000000000000113686837721616</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="21">
@@ -4514,31 +4514,31 @@
         <v>11.8291026747245</v>
       </c>
       <c r="C21" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
       <c r="D21" t="n">
-        <v>268.404470424806</v>
+        <v>268.404470383308</v>
       </c>
       <c r="E21" t="n">
-        <v>966.60440156832</v>
+        <v>966.604401385309</v>
       </c>
       <c r="F21" t="n">
         <v>880.419322745562</v>
       </c>
       <c r="G21" t="n">
-        <v>-86.1850788227581</v>
+        <v>-86.1850786397468</v>
       </c>
       <c r="H21" t="n">
-        <v>-21.1870778365856</v>
+        <v>-21.1870777203114</v>
       </c>
       <c r="I21" t="n">
-        <v>247.21739258822</v>
+        <v>247.217392662996</v>
       </c>
       <c r="J21" t="n">
-        <v>880.419322745562</v>
+        <v>880.419322745563</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.000000000000113686837721616</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="22">
@@ -4549,31 +4549,31 @@
         <v>10.8405558524574</v>
       </c>
       <c r="C22" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
       <c r="D22" t="n">
-        <v>249.143528193323</v>
+        <v>249.14352802219</v>
       </c>
       <c r="E22" t="n">
-        <v>982.909239763582</v>
+        <v>982.909239076875</v>
       </c>
       <c r="F22" t="n">
         <v>903.254550237668</v>
       </c>
       <c r="G22" t="n">
-        <v>-79.6546895259138</v>
+        <v>-79.6546888392069</v>
       </c>
       <c r="H22" t="n">
-        <v>-20.3100409917055</v>
+        <v>-20.3100408467772</v>
       </c>
       <c r="I22" t="n">
-        <v>228.833487201618</v>
+        <v>228.833487175413</v>
       </c>
       <c r="J22" t="n">
         <v>903.254550237669</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.00000000000102318153949454</v>
       </c>
     </row>
     <row r="23">
@@ -4584,31 +4584,31 @@
         <v>10.4064097033053</v>
       </c>
       <c r="C23" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
       <c r="D23" t="n">
-        <v>242.785987033018</v>
+        <v>242.785986860874</v>
       </c>
       <c r="E23" t="n">
-        <v>982.909239763582</v>
+        <v>982.909239076875</v>
       </c>
       <c r="F23" t="n">
         <v>903.254550237668</v>
       </c>
       <c r="G23" t="n">
-        <v>-79.6546895259138</v>
+        <v>-79.6546888392069</v>
       </c>
       <c r="H23" t="n">
-        <v>-19.8006788096626</v>
+        <v>-19.8006786425733</v>
       </c>
       <c r="I23" t="n">
-        <v>222.985308223356</v>
+        <v>222.985308218301</v>
       </c>
       <c r="J23" t="n">
         <v>903.254550237669</v>
       </c>
       <c r="K23" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.00000000000102318153949454</v>
       </c>
     </row>
     <row r="24">
@@ -4619,31 +4619,31 @@
         <v>9.30124144311374</v>
       </c>
       <c r="C24" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
       <c r="D24" t="n">
-        <v>226.602144985928</v>
+        <v>226.602144811209</v>
       </c>
       <c r="E24" t="n">
-        <v>982.909239763582</v>
+        <v>982.909239076875</v>
       </c>
       <c r="F24" t="n">
         <v>903.254550237668</v>
       </c>
       <c r="G24" t="n">
-        <v>-79.6546895259138</v>
+        <v>-79.6546888392069</v>
       </c>
       <c r="H24" t="n">
-        <v>-19.658991290457</v>
+        <v>-19.6589911076995</v>
       </c>
       <c r="I24" t="n">
-        <v>206.943153695471</v>
+        <v>206.94315370351</v>
       </c>
       <c r="J24" t="n">
         <v>903.254550237669</v>
       </c>
       <c r="K24" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.00000000000102318153949454</v>
       </c>
     </row>
     <row r="25">
@@ -4654,31 +4654,31 @@
         <v>11.8808644507488</v>
       </c>
       <c r="C25" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
       <c r="D25" t="n">
-        <v>264.377579551313</v>
+        <v>264.377579382602</v>
       </c>
       <c r="E25" t="n">
-        <v>982.909239763582</v>
+        <v>982.909239076875</v>
       </c>
       <c r="F25" t="n">
         <v>903.254550237668</v>
       </c>
       <c r="G25" t="n">
-        <v>-79.6546895259138</v>
+        <v>-79.6546888392069</v>
       </c>
       <c r="H25" t="n">
-        <v>-19.8849784340886</v>
+        <v>-19.8849782421559</v>
       </c>
       <c r="I25" t="n">
-        <v>244.492601117224</v>
+        <v>244.492601140446</v>
       </c>
       <c r="J25" t="n">
         <v>903.254550237669</v>
       </c>
       <c r="K25" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.00000000000102318153949454</v>
       </c>
     </row>
     <row r="26">
@@ -4689,31 +4689,31 @@
         <v>11.4067396261152</v>
       </c>
       <c r="C26" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
       <c r="D26" t="n">
-        <v>256.438846399562</v>
+        <v>256.438846202921</v>
       </c>
       <c r="E26" t="n">
-        <v>946.734943713259</v>
+        <v>946.73494291413</v>
       </c>
       <c r="F26" t="n">
         <v>877.295317819317</v>
       </c>
       <c r="G26" t="n">
-        <v>-69.439625893942</v>
+        <v>-69.4396250948131</v>
       </c>
       <c r="H26" t="n">
-        <v>-20.4786402405574</v>
+        <v>-20.4786400459425</v>
       </c>
       <c r="I26" t="n">
-        <v>235.960206159004</v>
+        <v>235.960206156979</v>
       </c>
       <c r="J26" t="n">
-        <v>877.295317819317</v>
+        <v>877.295317819318</v>
       </c>
       <c r="K26" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="27">
@@ -4724,31 +4724,31 @@
         <v>9.28905311211552</v>
       </c>
       <c r="C27" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
       <c r="D27" t="n">
-        <v>225.427908714937</v>
+        <v>225.427908513365</v>
       </c>
       <c r="E27" t="n">
-        <v>946.734943713259</v>
+        <v>946.73494291413</v>
       </c>
       <c r="F27" t="n">
         <v>877.295317819317</v>
       </c>
       <c r="G27" t="n">
-        <v>-69.439625893942</v>
+        <v>-69.4396250948131</v>
       </c>
       <c r="H27" t="n">
-        <v>-19.4686114563161</v>
+        <v>-19.4686112585613</v>
       </c>
       <c r="I27" t="n">
-        <v>205.959297258621</v>
+        <v>205.959297254804</v>
       </c>
       <c r="J27" t="n">
-        <v>877.295317819317</v>
+        <v>877.295317819318</v>
       </c>
       <c r="K27" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="28">
@@ -4759,31 +4759,31 @@
         <v>9.01117566522454</v>
       </c>
       <c r="C28" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
       <c r="D28" t="n">
-        <v>221.358732218543</v>
+        <v>221.358732016324</v>
       </c>
       <c r="E28" t="n">
-        <v>946.734943713259</v>
+        <v>946.73494291413</v>
       </c>
       <c r="F28" t="n">
         <v>877.295317819317</v>
       </c>
       <c r="G28" t="n">
-        <v>-69.439625893942</v>
+        <v>-69.4396250948131</v>
       </c>
       <c r="H28" t="n">
-        <v>-16.8548920813648</v>
+        <v>-16.8548918800125</v>
       </c>
       <c r="I28" t="n">
-        <v>204.503840137178</v>
+        <v>204.503840136311</v>
       </c>
       <c r="J28" t="n">
-        <v>877.295317819317</v>
+        <v>877.295317819318</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="29">
@@ -4794,31 +4794,31 @@
         <v>10.5238126035059</v>
       </c>
       <c r="C29" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
       <c r="D29" t="n">
-        <v>243.509456380217</v>
+        <v>243.50945618152</v>
       </c>
       <c r="E29" t="n">
-        <v>946.734943713259</v>
+        <v>946.73494291413</v>
       </c>
       <c r="F29" t="n">
         <v>877.295317819317</v>
       </c>
       <c r="G29" t="n">
-        <v>-69.439625893942</v>
+        <v>-69.4396250948131</v>
       </c>
       <c r="H29" t="n">
-        <v>-12.6374821157034</v>
+        <v>-12.6374819102959</v>
       </c>
       <c r="I29" t="n">
-        <v>230.871974264513</v>
+        <v>230.871974271224</v>
       </c>
       <c r="J29" t="n">
-        <v>877.295317819317</v>
+        <v>877.295317819318</v>
       </c>
       <c r="K29" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="30">
@@ -4829,31 +4829,31 @@
         <v>11.9127471155729</v>
       </c>
       <c r="C30" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
       <c r="D30" t="n">
-        <v>264.340859490404</v>
+        <v>264.340859308385</v>
       </c>
       <c r="E30" t="n">
-        <v>984.405025722755</v>
+        <v>984.405024983075</v>
       </c>
       <c r="F30" t="n">
         <v>983.824617972529</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.580407750225618</v>
+        <v>-0.580407010545628</v>
       </c>
       <c r="H30" t="n">
-        <v>-6.81638155933195</v>
+        <v>-6.81638134941163</v>
       </c>
       <c r="I30" t="n">
-        <v>257.524477931073</v>
+        <v>257.524477958973</v>
       </c>
       <c r="J30" t="n">
         <v>983.82461797253</v>
       </c>
       <c r="K30" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="31">
@@ -4864,31 +4864,31 @@
         <v>10.8348612881606</v>
       </c>
       <c r="C31" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
       <c r="D31" t="n">
-        <v>248.556535415974</v>
+        <v>248.556535231444</v>
       </c>
       <c r="E31" t="n">
-        <v>984.405025722755</v>
+        <v>984.405024983075</v>
       </c>
       <c r="F31" t="n">
         <v>983.824617972529</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.580407750225618</v>
+        <v>-0.580407010545628</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.81942948807312</v>
+        <v>-1.81942928634774</v>
       </c>
       <c r="I31" t="n">
-        <v>246.737105927901</v>
+        <v>246.737105945096</v>
       </c>
       <c r="J31" t="n">
         <v>983.82461797253</v>
       </c>
       <c r="K31" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="32">
@@ -4899,31 +4899,31 @@
         <v>9.02929647186484</v>
       </c>
       <c r="C32" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
       <c r="D32" t="n">
-        <v>222.116239539534</v>
+        <v>222.1162393508</v>
       </c>
       <c r="E32" t="n">
-        <v>984.405025722755</v>
+        <v>984.405024983075</v>
       </c>
       <c r="F32" t="n">
         <v>983.824617972529</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.580407750225618</v>
+        <v>-0.580407010545628</v>
       </c>
       <c r="H32" t="n">
-        <v>2.35337409807307</v>
+        <v>2.35337427889575</v>
       </c>
       <c r="I32" t="n">
-        <v>224.469613637607</v>
+        <v>224.469613629695</v>
       </c>
       <c r="J32" t="n">
         <v>983.82461797253</v>
       </c>
       <c r="K32" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="33">
@@ -4934,31 +4934,31 @@
         <v>10.8918722375126</v>
       </c>
       <c r="C33" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
       <c r="D33" t="n">
-        <v>249.391391276843</v>
+        <v>249.391391092446</v>
       </c>
       <c r="E33" t="n">
-        <v>984.405025722755</v>
+        <v>984.405024983075</v>
       </c>
       <c r="F33" t="n">
         <v>983.824617972529</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.580407750225618</v>
+        <v>-0.580407010545628</v>
       </c>
       <c r="H33" t="n">
-        <v>5.70202919910663</v>
+        <v>5.70202934631884</v>
       </c>
       <c r="I33" t="n">
-        <v>255.09342047595</v>
+        <v>255.093420438765</v>
       </c>
       <c r="J33" t="n">
         <v>983.82461797253</v>
       </c>
       <c r="K33" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="34">
@@ -4969,31 +4969,31 @@
         <v>10.2441206518659</v>
       </c>
       <c r="C34" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
       <c r="D34" t="n">
-        <v>245.499189518779</v>
+        <v>245.49918948061</v>
       </c>
       <c r="E34" t="n">
-        <v>1006.2086779093</v>
+        <v>1006.20867776047</v>
       </c>
       <c r="F34" t="n">
         <v>1037.6039560867</v>
       </c>
       <c r="G34" t="n">
-        <v>31.3952781773999</v>
+        <v>31.3952783262273</v>
       </c>
       <c r="H34" t="n">
-        <v>8.22653581502753</v>
+        <v>8.22653591592153</v>
       </c>
       <c r="I34" t="n">
-        <v>253.725725333807</v>
+        <v>253.725725396531</v>
       </c>
       <c r="J34" t="n">
         <v>1037.6039560867</v>
       </c>
       <c r="K34" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="35">
@@ -5004,31 +5004,31 @@
         <v>10.4852423350932</v>
       </c>
       <c r="C35" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
       <c r="D35" t="n">
-        <v>249.030122659045</v>
+        <v>249.030122621437</v>
       </c>
       <c r="E35" t="n">
-        <v>1006.2086779093</v>
+        <v>1006.20867776047</v>
       </c>
       <c r="F35" t="n">
         <v>1037.6039560867</v>
       </c>
       <c r="G35" t="n">
-        <v>31.3952781773999</v>
+        <v>31.3952783262273</v>
       </c>
       <c r="H35" t="n">
-        <v>9.0852519531249</v>
+        <v>9.08525201001684</v>
       </c>
       <c r="I35" t="n">
-        <v>258.11537461217</v>
+        <v>258.115374631454</v>
       </c>
       <c r="J35" t="n">
         <v>1037.6039560867</v>
       </c>
       <c r="K35" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="36">
@@ -5039,31 +5039,31 @@
         <v>10.721518519552</v>
       </c>
       <c r="C36" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
       <c r="D36" t="n">
-        <v>252.490099376172</v>
+        <v>252.490099339114</v>
       </c>
       <c r="E36" t="n">
-        <v>1006.2086779093</v>
+        <v>1006.20867776047</v>
       </c>
       <c r="F36" t="n">
         <v>1037.6039560867</v>
       </c>
       <c r="G36" t="n">
-        <v>31.3952781773999</v>
+        <v>31.3952783262273</v>
       </c>
       <c r="H36" t="n">
-        <v>8.27817761339875</v>
+        <v>8.27817762860477</v>
       </c>
       <c r="I36" t="n">
-        <v>260.768276989571</v>
+        <v>260.768276967719</v>
       </c>
       <c r="J36" t="n">
         <v>1037.6039560867</v>
       </c>
       <c r="K36" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="37">
@@ -5074,31 +5074,31 @@
         <v>11.1789937404245</v>
       </c>
       <c r="C37" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
       <c r="D37" t="n">
-        <v>259.189266355302</v>
+        <v>259.18926631931</v>
       </c>
       <c r="E37" t="n">
-        <v>1006.2086779093</v>
+        <v>1006.20867776047</v>
       </c>
       <c r="F37" t="n">
         <v>1037.6039560867</v>
       </c>
       <c r="G37" t="n">
-        <v>31.3952781773999</v>
+        <v>31.3952783262273</v>
       </c>
       <c r="H37" t="n">
-        <v>5.80531279584905</v>
+        <v>5.80531277168531</v>
       </c>
       <c r="I37" t="n">
-        <v>264.994579151152</v>
+        <v>264.994579090995</v>
       </c>
       <c r="J37" t="n">
         <v>1037.6039560867</v>
       </c>
       <c r="K37" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="38">
@@ -5109,31 +5109,31 @@
         <v>11.3312759206842</v>
       </c>
       <c r="C38" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
       <c r="D38" t="n">
-        <v>265.711238810759</v>
+        <v>265.711238888836</v>
       </c>
       <c r="E38" t="n">
-        <v>1095.38451461588</v>
+        <v>1095.38451493337</v>
       </c>
       <c r="F38" t="n">
         <v>1091.14065395875</v>
       </c>
       <c r="G38" t="n">
-        <v>-4.24386065713634</v>
+        <v>-4.24386097461911</v>
       </c>
       <c r="H38" t="n">
-        <v>1.66665750047582</v>
+        <v>1.66665743925845</v>
       </c>
       <c r="I38" t="n">
-        <v>267.377896311235</v>
+        <v>267.377896328095</v>
       </c>
       <c r="J38" t="n">
         <v>1091.14065395875</v>
       </c>
       <c r="K38" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="39">
@@ -5144,31 +5144,31 @@
         <v>12.1178813133434</v>
       </c>
       <c r="C39" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
       <c r="D39" t="n">
-        <v>277.230115968866</v>
+        <v>277.230116048775</v>
       </c>
       <c r="E39" t="n">
-        <v>1095.38451461588</v>
+        <v>1095.38451493337</v>
       </c>
       <c r="F39" t="n">
         <v>1091.14065395875</v>
       </c>
       <c r="G39" t="n">
-        <v>-4.24386065713634</v>
+        <v>-4.24386097461911</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0798536835774</v>
+        <v>-1.07985376687747</v>
       </c>
       <c r="I39" t="n">
-        <v>276.150262285289</v>
+        <v>276.150262281898</v>
       </c>
       <c r="J39" t="n">
         <v>1091.14065395875</v>
       </c>
       <c r="K39" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="40">
@@ -5179,31 +5179,31 @@
         <v>10.4589062836713</v>
       </c>
       <c r="C40" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
       <c r="D40" t="n">
-        <v>252.936448834753</v>
+        <v>252.936448910799</v>
       </c>
       <c r="E40" t="n">
-        <v>1095.38451461588</v>
+        <v>1095.38451493337</v>
       </c>
       <c r="F40" t="n">
         <v>1091.14065395875</v>
       </c>
       <c r="G40" t="n">
-        <v>-4.24386065713634</v>
+        <v>-4.24386097461911</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.43422075631063</v>
+        <v>-2.43422084672246</v>
       </c>
       <c r="I40" t="n">
-        <v>250.502228078443</v>
+        <v>250.502228064076</v>
       </c>
       <c r="J40" t="n">
         <v>1091.14065395875</v>
       </c>
       <c r="K40" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="41">
@@ -5214,31 +5214,31 @@
         <v>13.6391137687502</v>
       </c>
       <c r="C41" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
       <c r="D41" t="n">
-        <v>299.506711001504</v>
+        <v>299.506711084956</v>
       </c>
       <c r="E41" t="n">
-        <v>1095.38451461588</v>
+        <v>1095.38451493337</v>
       </c>
       <c r="F41" t="n">
         <v>1091.14065395875</v>
       </c>
       <c r="G41" t="n">
-        <v>-4.24386065713634</v>
+        <v>-4.24386097461911</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.39644371772385</v>
+        <v>-2.39644380027652</v>
       </c>
       <c r="I41" t="n">
-        <v>297.11026728378</v>
+        <v>297.110267284679</v>
       </c>
       <c r="J41" t="n">
         <v>1091.14065395875</v>
       </c>
       <c r="K41" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="42">
@@ -5249,31 +5249,31 @@
         <v>11.6428691387851</v>
       </c>
       <c r="C42" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
       <c r="D42" t="n">
-        <v>268.815456209385</v>
+        <v>268.815456248638</v>
       </c>
       <c r="E42" t="n">
-        <v>1163.12471065778</v>
+        <v>1163.12471082877</v>
       </c>
       <c r="F42" t="n">
         <v>1143.08791762752</v>
       </c>
       <c r="G42" t="n">
-        <v>-20.0367930302639</v>
+        <v>-20.0367932012502</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.966522567817062</v>
+        <v>-0.966522627539652</v>
       </c>
       <c r="I42" t="n">
-        <v>267.848933641568</v>
+        <v>267.848933621099</v>
       </c>
       <c r="J42" t="n">
         <v>1143.08791762752</v>
       </c>
       <c r="K42" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="43">
@@ -5284,31 +5284,31 @@
         <v>12.3919304064259</v>
       </c>
       <c r="C43" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
       <c r="D43" t="n">
-        <v>279.784545420281</v>
+        <v>279.784545461279</v>
       </c>
       <c r="E43" t="n">
-        <v>1163.12471065778</v>
+        <v>1163.12471082877</v>
       </c>
       <c r="F43" t="n">
         <v>1143.08791762752</v>
       </c>
       <c r="G43" t="n">
-        <v>-20.0367930302639</v>
+        <v>-20.0367932012502</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.01162438375388</v>
+        <v>-2.01162442755394</v>
       </c>
       <c r="I43" t="n">
-        <v>277.772921036527</v>
+        <v>277.772921033725</v>
       </c>
       <c r="J43" t="n">
         <v>1143.08791762752</v>
       </c>
       <c r="K43" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="44">
@@ -5319,31 +5319,31 @@
         <v>11.7483984681507</v>
       </c>
       <c r="C44" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
       <c r="D44" t="n">
-        <v>270.360804605014</v>
+        <v>270.360804644513</v>
       </c>
       <c r="E44" t="n">
-        <v>1163.12471065778</v>
+        <v>1163.12471082877</v>
       </c>
       <c r="F44" t="n">
         <v>1143.08791762752</v>
       </c>
       <c r="G44" t="n">
-        <v>-20.0367930302639</v>
+        <v>-20.0367932012502</v>
       </c>
       <c r="H44" t="n">
-        <v>-5.5317491655343</v>
+        <v>-5.5317492003194</v>
       </c>
       <c r="I44" t="n">
-        <v>264.82905543948</v>
+        <v>264.829055444194</v>
       </c>
       <c r="J44" t="n">
         <v>1143.08791762752</v>
       </c>
       <c r="K44" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="45">
@@ -5354,31 +5354,31 @@
         <v>16.7882921587443</v>
       </c>
       <c r="C45" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
       <c r="D45" t="n">
-        <v>344.163904423099</v>
+        <v>344.163904474335</v>
       </c>
       <c r="E45" t="n">
-        <v>1163.12471065778</v>
+        <v>1163.12471082877</v>
       </c>
       <c r="F45" t="n">
         <v>1143.08791762752</v>
       </c>
       <c r="G45" t="n">
-        <v>-20.0367930302639</v>
+        <v>-20.0367932012502</v>
       </c>
       <c r="H45" t="n">
-        <v>-11.5268969131583</v>
+        <v>-11.526896945836</v>
       </c>
       <c r="I45" t="n">
-        <v>332.63700750994</v>
+        <v>332.637007528499</v>
       </c>
       <c r="J45" t="n">
         <v>1143.08791762752</v>
       </c>
       <c r="K45" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000113686837721616</v>
       </c>
     </row>
     <row r="46">
@@ -5389,31 +5389,31 @@
         <v>12.7515959096748</v>
       </c>
       <c r="C46" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
       <c r="D46" t="n">
-        <v>283.343453226163</v>
+        <v>283.343453221826</v>
       </c>
       <c r="E46" t="n">
-        <v>1205.22372965045</v>
+        <v>1205.22372964453</v>
       </c>
       <c r="F46" t="n">
         <v>1114.90897830289</v>
       </c>
       <c r="G46" t="n">
-        <v>-90.3147513475685</v>
+        <v>-90.314751341645</v>
       </c>
       <c r="H46" t="n">
-        <v>-19.9970676266259</v>
+        <v>-19.9970676641038</v>
       </c>
       <c r="I46" t="n">
-        <v>263.346385599537</v>
+        <v>263.346385557722</v>
       </c>
       <c r="J46" t="n">
         <v>1114.90897830289</v>
       </c>
       <c r="K46" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="47">
@@ -5424,31 +5424,31 @@
         <v>14.4607563865404</v>
       </c>
       <c r="C47" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
       <c r="D47" t="n">
-        <v>308.372025061849</v>
+        <v>308.372025061491</v>
       </c>
       <c r="E47" t="n">
-        <v>1205.22372965045</v>
+        <v>1205.22372964453</v>
       </c>
       <c r="F47" t="n">
         <v>1114.90897830289</v>
       </c>
       <c r="G47" t="n">
-        <v>-90.3147513475685</v>
+        <v>-90.314751341645</v>
       </c>
       <c r="H47" t="n">
-        <v>-24.4177839961194</v>
+        <v>-24.4177840199338</v>
       </c>
       <c r="I47" t="n">
-        <v>283.954241065729</v>
+        <v>283.954241041558</v>
       </c>
       <c r="J47" t="n">
         <v>1114.90897830289</v>
       </c>
       <c r="K47" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="48">
@@ -5459,31 +5459,31 @@
         <v>12.94756273816</v>
       </c>
       <c r="C48" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
       <c r="D48" t="n">
-        <v>286.213148559364</v>
+        <v>286.213148555483</v>
       </c>
       <c r="E48" t="n">
-        <v>1205.22372965045</v>
+        <v>1205.22372964453</v>
       </c>
       <c r="F48" t="n">
         <v>1114.90897830289</v>
       </c>
       <c r="G48" t="n">
-        <v>-90.3147513475685</v>
+        <v>-90.314751341645</v>
       </c>
       <c r="H48" t="n">
-        <v>-24.7890460216388</v>
+        <v>-24.7890460133259</v>
       </c>
       <c r="I48" t="n">
-        <v>261.424102537725</v>
+        <v>261.424102542157</v>
       </c>
       <c r="J48" t="n">
         <v>1114.90897830289</v>
       </c>
       <c r="K48" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="49">
@@ -5494,31 +5494,31 @@
         <v>15.7529825985791</v>
       </c>
       <c r="C49" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
       <c r="D49" t="n">
-        <v>327.295102803078</v>
+        <v>327.295102805731</v>
       </c>
       <c r="E49" t="n">
-        <v>1205.22372965045</v>
+        <v>1205.22372964453</v>
       </c>
       <c r="F49" t="n">
         <v>1114.90897830289</v>
       </c>
       <c r="G49" t="n">
-        <v>-90.3147513475685</v>
+        <v>-90.314751341645</v>
       </c>
       <c r="H49" t="n">
-        <v>-21.110853703184</v>
+        <v>-21.1108536442802</v>
       </c>
       <c r="I49" t="n">
-        <v>306.184249099894</v>
+        <v>306.18424916145</v>
       </c>
       <c r="J49" t="n">
         <v>1114.90897830289</v>
       </c>
       <c r="K49" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="50">
@@ -5529,31 +5529,31 @@
         <v>13.3986549446632</v>
       </c>
       <c r="C50" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
       <c r="D50" t="n">
-        <v>286.729421939569</v>
+        <v>286.729421774797</v>
       </c>
       <c r="E50" t="n">
-        <v>1253.37371688426</v>
+        <v>1253.3737162421</v>
       </c>
       <c r="F50" t="n">
         <v>1266.59424936741</v>
       </c>
       <c r="G50" t="n">
-        <v>13.2205324831477</v>
+        <v>13.2205331253069</v>
       </c>
       <c r="H50" t="n">
-        <v>-13.3832070407551</v>
+        <v>-13.3832069127967</v>
       </c>
       <c r="I50" t="n">
-        <v>273.346214898814</v>
+        <v>273.346214862</v>
       </c>
       <c r="J50" t="n">
         <v>1266.59424936741</v>
       </c>
       <c r="K50" t="n">
-        <v>0.000000000000682121026329696</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="51">
@@ -5564,31 +5564,31 @@
         <v>16.7879730089583</v>
       </c>
       <c r="C51" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
       <c r="D51" t="n">
-        <v>336.361853647656</v>
+        <v>336.361853490777</v>
       </c>
       <c r="E51" t="n">
-        <v>1253.37371688426</v>
+        <v>1253.3737162421</v>
       </c>
       <c r="F51" t="n">
         <v>1266.59424936741</v>
       </c>
       <c r="G51" t="n">
-        <v>13.2205324831477</v>
+        <v>13.2205331253069</v>
       </c>
       <c r="H51" t="n">
-        <v>-3.61681231116663</v>
+        <v>-3.61681214255376</v>
       </c>
       <c r="I51" t="n">
-        <v>332.745041336489</v>
+        <v>332.745041348223</v>
       </c>
       <c r="J51" t="n">
         <v>1266.59424936741</v>
       </c>
       <c r="K51" t="n">
-        <v>0.000000000000682121026329696</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="52">
@@ -5599,31 +5599,31 @@
         <v>13.3007279982884</v>
       </c>
       <c r="C52" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
       <c r="D52" t="n">
-        <v>285.295401176061</v>
+        <v>285.295401011061</v>
       </c>
       <c r="E52" t="n">
-        <v>1253.37371688426</v>
+        <v>1253.3737162421</v>
       </c>
       <c r="F52" t="n">
         <v>1266.59424936741</v>
       </c>
       <c r="G52" t="n">
-        <v>13.2205324831477</v>
+        <v>13.2205331253069</v>
       </c>
       <c r="H52" t="n">
-        <v>8.18833048558134</v>
+        <v>8.18833066644859</v>
       </c>
       <c r="I52" t="n">
-        <v>293.483731661643</v>
+        <v>293.48373167751</v>
       </c>
       <c r="J52" t="n">
         <v>1266.59424936741</v>
       </c>
       <c r="K52" t="n">
-        <v>0.000000000000682121026329696</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="53">
@@ -5634,31 +5634,31 @@
         <v>17.3769729695861</v>
       </c>
       <c r="C53" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
       <c r="D53" t="n">
-        <v>344.987040120973</v>
+        <v>344.987039965465</v>
       </c>
       <c r="E53" t="n">
-        <v>1253.37371688426</v>
+        <v>1253.3737162421</v>
       </c>
       <c r="F53" t="n">
         <v>1266.59424936741</v>
       </c>
       <c r="G53" t="n">
-        <v>13.2205324831477</v>
+        <v>13.2205331253069</v>
       </c>
       <c r="H53" t="n">
-        <v>22.0322213494888</v>
+        <v>22.0322215142104</v>
       </c>
       <c r="I53" t="n">
-        <v>367.019261470462</v>
+        <v>367.019261479676</v>
       </c>
       <c r="J53" t="n">
         <v>1266.59424936741</v>
       </c>
       <c r="K53" t="n">
-        <v>0.000000000000682121026329696</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="54">
@@ -5669,31 +5669,31 @@
         <v>16.0192758607371</v>
       </c>
       <c r="C54" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
       <c r="D54" t="n">
-        <v>331.357940202372</v>
+        <v>331.357940208446</v>
       </c>
       <c r="E54" t="n">
-        <v>1338.03601605366</v>
+        <v>1338.03601607995</v>
       </c>
       <c r="F54" t="n">
         <v>1501.18066181495</v>
       </c>
       <c r="G54" t="n">
-        <v>163.144645761298</v>
+        <v>163.144645735</v>
       </c>
       <c r="H54" t="n">
-        <v>37.9148602805559</v>
+        <v>37.9148604007316</v>
       </c>
       <c r="I54" t="n">
-        <v>369.272800482928</v>
+        <v>369.272800609177</v>
       </c>
       <c r="J54" t="n">
         <v>1501.18066181496</v>
       </c>
       <c r="K54" t="n">
-        <v>0.000000000000682121026329696</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="55">
@@ -5704,31 +5704,31 @@
         <v>18.0480441521233</v>
       </c>
       <c r="C55" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
       <c r="D55" t="n">
-        <v>361.066778901965</v>
+        <v>361.066778912763</v>
       </c>
       <c r="E55" t="n">
-        <v>1338.03601605366</v>
+        <v>1338.03601607995</v>
       </c>
       <c r="F55" t="n">
         <v>1501.18066181495</v>
       </c>
       <c r="G55" t="n">
-        <v>163.144645761298</v>
+        <v>163.144645735</v>
       </c>
       <c r="H55" t="n">
-        <v>45.4164363168902</v>
+        <v>45.4164363685476</v>
       </c>
       <c r="I55" t="n">
-        <v>406.483215218855</v>
+        <v>406.48321528131</v>
       </c>
       <c r="J55" t="n">
         <v>1501.18066181496</v>
       </c>
       <c r="K55" t="n">
-        <v>0.000000000000682121026329696</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="56">
@@ -5739,31 +5739,31 @@
         <v>14.8314652467803</v>
       </c>
       <c r="C56" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
       <c r="D56" t="n">
-        <v>313.963901619683</v>
+        <v>313.96390162299</v>
       </c>
       <c r="E56" t="n">
-        <v>1338.03601605366</v>
+        <v>1338.03601607995</v>
       </c>
       <c r="F56" t="n">
         <v>1501.18066181495</v>
       </c>
       <c r="G56" t="n">
-        <v>163.144645761298</v>
+        <v>163.144645735</v>
       </c>
       <c r="H56" t="n">
-        <v>44.5369494584918</v>
+        <v>44.5369494176583</v>
       </c>
       <c r="I56" t="n">
-        <v>358.500851078175</v>
+        <v>358.500851040648</v>
       </c>
       <c r="J56" t="n">
         <v>1501.18066181496</v>
       </c>
       <c r="K56" t="n">
-        <v>0.000000000000682121026329696</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="57">
@@ -5774,31 +5774,31 @@
         <v>16.0390422807548</v>
       </c>
       <c r="C57" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
       <c r="D57" t="n">
-        <v>331.647395329636</v>
+        <v>331.647395335756</v>
       </c>
       <c r="E57" t="n">
-        <v>1338.03601605366</v>
+        <v>1338.03601607995</v>
       </c>
       <c r="F57" t="n">
         <v>1501.18066181495</v>
       </c>
       <c r="G57" t="n">
-        <v>163.144645761298</v>
+        <v>163.144645735</v>
       </c>
       <c r="H57" t="n">
-        <v>35.2763997053607</v>
+        <v>35.2763995480638</v>
       </c>
       <c r="I57" t="n">
-        <v>366.923795034997</v>
+        <v>366.92379488382</v>
       </c>
       <c r="J57" t="n">
         <v>1501.18066181496</v>
       </c>
       <c r="K57" t="n">
-        <v>0.000000000000682121026329696</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="58">
@@ -5809,31 +5809,31 @@
         <v>0.0977424856544318</v>
       </c>
       <c r="C58" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
       <c r="D58" t="n">
-        <v>112.021250097792</v>
+        <v>112.021250432033</v>
       </c>
       <c r="E58" t="n">
-        <v>1160.55510401734</v>
+        <v>1160.55510546761</v>
       </c>
       <c r="F58" t="n">
         <v>1135.26047112508</v>
       </c>
       <c r="G58" t="n">
-        <v>-25.2946328922592</v>
+        <v>-25.2946343425258</v>
       </c>
       <c r="H58" t="n">
-        <v>17.6347870574969</v>
+        <v>17.6347867597641</v>
       </c>
       <c r="I58" t="n">
-        <v>129.656037155289</v>
+        <v>129.656037191797</v>
       </c>
       <c r="J58" t="n">
-        <v>1135.26047112508</v>
+        <v>1135.26047112509</v>
       </c>
       <c r="K58" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="59">
@@ -5844,31 +5844,31 @@
         <v>14.0447704192465</v>
       </c>
       <c r="C59" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
       <c r="D59" t="n">
-        <v>316.25847372607</v>
+        <v>316.258474092791</v>
       </c>
       <c r="E59" t="n">
-        <v>1160.55510401734</v>
+        <v>1160.55510546761</v>
       </c>
       <c r="F59" t="n">
         <v>1135.26047112508</v>
       </c>
       <c r="G59" t="n">
-        <v>-25.2946328922592</v>
+        <v>-25.2946343425258</v>
       </c>
       <c r="H59" t="n">
-        <v>0.994763886126776</v>
+        <v>0.994763506286155</v>
       </c>
       <c r="I59" t="n">
-        <v>317.253237612197</v>
+        <v>317.253237599077</v>
       </c>
       <c r="J59" t="n">
-        <v>1135.26047112508</v>
+        <v>1135.26047112509</v>
       </c>
       <c r="K59" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="60">
@@ -5879,31 +5879,31 @@
         <v>17.2785456875479</v>
       </c>
       <c r="C60" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
       <c r="D60" t="n">
-        <v>363.613170782705</v>
+        <v>363.613171156956</v>
       </c>
       <c r="E60" t="n">
-        <v>1160.55510401734</v>
+        <v>1160.55510546761</v>
       </c>
       <c r="F60" t="n">
         <v>1135.26047112508</v>
       </c>
       <c r="G60" t="n">
-        <v>-25.2946328922592</v>
+        <v>-25.2946343425258</v>
       </c>
       <c r="H60" t="n">
-        <v>-14.6436698087497</v>
+        <v>-14.6436702123701</v>
       </c>
       <c r="I60" t="n">
-        <v>348.969500973955</v>
+        <v>348.969500944586</v>
       </c>
       <c r="J60" t="n">
-        <v>1135.26047112508</v>
+        <v>1135.26047112509</v>
       </c>
       <c r="K60" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="61">
@@ -5914,31 +5914,31 @@
         <v>17.6233363262596</v>
       </c>
       <c r="C61" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
       <c r="D61" t="n">
-        <v>368.662209410776</v>
+        <v>368.66220978583</v>
       </c>
       <c r="E61" t="n">
-        <v>1160.55510401734</v>
+        <v>1160.55510546761</v>
       </c>
       <c r="F61" t="n">
         <v>1135.26047112508</v>
       </c>
       <c r="G61" t="n">
-        <v>-25.2946328922592</v>
+        <v>-25.2946343425258</v>
       </c>
       <c r="H61" t="n">
-        <v>-29.2805140271326</v>
+        <v>-29.2805143962045</v>
       </c>
       <c r="I61" t="n">
-        <v>339.381695383643</v>
+        <v>339.381695389626</v>
       </c>
       <c r="J61" t="n">
-        <v>1135.26047112508</v>
+        <v>1135.26047112509</v>
       </c>
       <c r="K61" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="62">
@@ -5949,31 +5949,31 @@
         <v>17.868151976636</v>
       </c>
       <c r="C62" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
       <c r="D62" t="n">
-        <v>361.729883749951</v>
+        <v>361.729883849862</v>
       </c>
       <c r="E62" t="n">
-        <v>1496.31259840874</v>
+        <v>1496.31259881624</v>
       </c>
       <c r="F62" t="n">
         <v>1332.87034060975</v>
       </c>
       <c r="G62" t="n">
-        <v>-163.442257798988</v>
+        <v>-163.442258206487</v>
       </c>
       <c r="H62" t="n">
-        <v>-42.9157687690218</v>
+        <v>-42.9157690452173</v>
       </c>
       <c r="I62" t="n">
-        <v>318.814114980929</v>
+        <v>318.814114804645</v>
       </c>
       <c r="J62" t="n">
         <v>1332.87034060975</v>
       </c>
       <c r="K62" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="63">
@@ -5984,31 +5984,31 @@
         <v>19.0161167301949</v>
       </c>
       <c r="C63" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
       <c r="D63" t="n">
-        <v>378.540428276451</v>
+        <v>378.540428379035</v>
       </c>
       <c r="E63" t="n">
-        <v>1496.31259840874</v>
+        <v>1496.31259881624</v>
       </c>
       <c r="F63" t="n">
         <v>1332.87034060975</v>
       </c>
       <c r="G63" t="n">
-        <v>-163.442257798988</v>
+        <v>-163.442258206487</v>
       </c>
       <c r="H63" t="n">
-        <v>-47.5477889380675</v>
+        <v>-47.547789107384</v>
       </c>
       <c r="I63" t="n">
-        <v>330.992639338383</v>
+        <v>330.992639271651</v>
       </c>
       <c r="J63" t="n">
         <v>1332.87034060975</v>
       </c>
       <c r="K63" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="64">
@@ -6019,31 +6019,31 @@
         <v>19.6337210138089</v>
       </c>
       <c r="C64" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
       <c r="D64" t="n">
-        <v>387.584490193216</v>
+        <v>387.584490297239</v>
       </c>
       <c r="E64" t="n">
-        <v>1496.31259840874</v>
+        <v>1496.31259881624</v>
       </c>
       <c r="F64" t="n">
         <v>1332.87034060975</v>
       </c>
       <c r="G64" t="n">
-        <v>-163.442257798988</v>
+        <v>-163.442258206487</v>
       </c>
       <c r="H64" t="n">
-        <v>-43.1765745342698</v>
+        <v>-43.1765745827049</v>
       </c>
       <c r="I64" t="n">
-        <v>344.407915658947</v>
+        <v>344.407915714534</v>
       </c>
       <c r="J64" t="n">
         <v>1332.87034060975</v>
       </c>
       <c r="K64" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="65">
@@ -6054,31 +6054,31 @@
         <v>18.3275901782376</v>
       </c>
       <c r="C65" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
       <c r="D65" t="n">
-        <v>368.457796189122</v>
+        <v>368.457796290103</v>
       </c>
       <c r="E65" t="n">
-        <v>1496.31259840874</v>
+        <v>1496.31259881624</v>
       </c>
       <c r="F65" t="n">
         <v>1332.87034060975</v>
       </c>
       <c r="G65" t="n">
-        <v>-163.442257798988</v>
+        <v>-163.442258206487</v>
       </c>
       <c r="H65" t="n">
-        <v>-29.8021255576286</v>
+        <v>-29.8021254711798</v>
       </c>
       <c r="I65" t="n">
-        <v>338.655670631493</v>
+        <v>338.655670818923</v>
       </c>
       <c r="J65" t="n">
         <v>1332.87034060975</v>
       </c>
       <c r="K65" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000159161572810262</v>
       </c>
     </row>
     <row r="66">
@@ -6089,31 +6089,31 @@
         <v>18.0671285639402</v>
       </c>
       <c r="C66" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
       <c r="D66" t="n">
-        <v>350.411767062232</v>
+        <v>350.411766780816</v>
       </c>
       <c r="E66" t="n">
-        <v>1521.93167983099</v>
+        <v>1521.93167872446</v>
       </c>
       <c r="F66" t="n">
         <v>1543.75677367368</v>
       </c>
       <c r="G66" t="n">
-        <v>21.8250938426916</v>
+        <v>21.8250949492272</v>
       </c>
       <c r="H66" t="n">
-        <v>-7.42444200814399</v>
+        <v>-7.42444177280874</v>
       </c>
       <c r="I66" t="n">
-        <v>342.987325054088</v>
+        <v>342.987325008007</v>
       </c>
       <c r="J66" t="n">
         <v>1543.75677367368</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="67">
@@ -6124,31 +6124,31 @@
         <v>20.8122714076788</v>
       </c>
       <c r="C67" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
       <c r="D67" t="n">
-        <v>390.61103787016</v>
+        <v>390.611037595137</v>
       </c>
       <c r="E67" t="n">
-        <v>1521.93167983099</v>
+        <v>1521.93167872446</v>
       </c>
       <c r="F67" t="n">
         <v>1543.75677367368</v>
       </c>
       <c r="G67" t="n">
-        <v>21.8250938426916</v>
+        <v>21.8250949492272</v>
       </c>
       <c r="H67" t="n">
-        <v>6.67891759917661</v>
+        <v>6.67891791058597</v>
       </c>
       <c r="I67" t="n">
-        <v>397.289955469336</v>
+        <v>397.289955505723</v>
       </c>
       <c r="J67" t="n">
         <v>1543.75677367368</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="68">
@@ -6159,31 +6159,31 @@
         <v>19.5955177898177</v>
       </c>
       <c r="C68" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
       <c r="D68" t="n">
-        <v>372.793164274807</v>
+        <v>372.79316399695</v>
       </c>
       <c r="E68" t="n">
-        <v>1521.93167983099</v>
+        <v>1521.93167872446</v>
       </c>
       <c r="F68" t="n">
         <v>1543.75677367368</v>
       </c>
       <c r="G68" t="n">
-        <v>21.8250938426916</v>
+        <v>21.8250949492272</v>
       </c>
       <c r="H68" t="n">
-        <v>12.5079532643332</v>
+        <v>12.5079535790044</v>
       </c>
       <c r="I68" t="n">
-        <v>385.30111753914</v>
+        <v>385.301117575954</v>
       </c>
       <c r="J68" t="n">
         <v>1543.75677367368</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="69">
@@ -6194,31 +6194,31 @@
         <v>22.00763704929</v>
       </c>
       <c r="C69" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
       <c r="D69" t="n">
-        <v>408.115710623792</v>
+        <v>408.115710351553</v>
       </c>
       <c r="E69" t="n">
-        <v>1521.93167983099</v>
+        <v>1521.93167872446</v>
       </c>
       <c r="F69" t="n">
         <v>1543.75677367368</v>
       </c>
       <c r="G69" t="n">
-        <v>21.8250938426916</v>
+        <v>21.8250949492272</v>
       </c>
       <c r="H69" t="n">
-        <v>10.0626649873257</v>
+        <v>10.0626652324464</v>
       </c>
       <c r="I69" t="n">
-        <v>418.178375611118</v>
+        <v>418.178375583999</v>
       </c>
       <c r="J69" t="n">
         <v>1543.75677367368</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="70">
@@ -6229,31 +6229,31 @@
         <v>19.4336483530636</v>
       </c>
       <c r="C70" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
       <c r="D70" t="n">
-        <v>380.557882918532</v>
+        <v>380.557882907771</v>
       </c>
       <c r="E70" t="n">
-        <v>1668.96678242333</v>
+        <v>1668.96678240362</v>
       </c>
       <c r="F70" t="n">
         <v>1670.84147153657</v>
       </c>
       <c r="G70" t="n">
-        <v>1.87468911324186</v>
+        <v>1.87468913295083</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.656947231845839</v>
+        <v>-0.656947129087834</v>
       </c>
       <c r="I70" t="n">
-        <v>379.900935686686</v>
+        <v>379.900935778683</v>
       </c>
       <c r="J70" t="n">
         <v>1670.84147153657</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="71">
@@ -6264,31 +6264,31 @@
         <v>23.7715703226929</v>
       </c>
       <c r="C71" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
       <c r="D71" t="n">
-        <v>444.081462537908</v>
+        <v>444.08146253725</v>
       </c>
       <c r="E71" t="n">
-        <v>1668.96678242333</v>
+        <v>1668.96678240362</v>
       </c>
       <c r="F71" t="n">
         <v>1670.84147153657</v>
       </c>
       <c r="G71" t="n">
-        <v>1.87468911324186</v>
+        <v>1.87468913295083</v>
       </c>
       <c r="H71" t="n">
-        <v>-4.49454431545194</v>
+        <v>-4.49454430877124</v>
       </c>
       <c r="I71" t="n">
-        <v>439.586918222457</v>
+        <v>439.586918228478</v>
       </c>
       <c r="J71" t="n">
         <v>1670.84147153657</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="72">
@@ -6299,31 +6299,31 @@
         <v>20.6653025217431</v>
       </c>
       <c r="C72" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
       <c r="D72" t="n">
-        <v>398.593956917884</v>
+        <v>398.593956909991</v>
       </c>
       <c r="E72" t="n">
-        <v>1668.96678242333</v>
+        <v>1668.96678240362</v>
       </c>
       <c r="F72" t="n">
         <v>1670.84147153657</v>
       </c>
       <c r="G72" t="n">
-        <v>1.87468911324186</v>
+        <v>1.87468913295083</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.45012626349262</v>
+        <v>-1.45012630660378</v>
       </c>
       <c r="I72" t="n">
-        <v>397.143830654391</v>
+        <v>397.143830603387</v>
       </c>
       <c r="J72" t="n">
         <v>1670.84147153657</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="73">
@@ -6334,31 +6334,31 @@
         <v>23.8843839125212</v>
       </c>
       <c r="C73" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
       <c r="D73" t="n">
-        <v>445.733480049007</v>
+        <v>445.73348004861</v>
       </c>
       <c r="E73" t="n">
-        <v>1668.96678242333</v>
+        <v>1668.96678240362</v>
       </c>
       <c r="F73" t="n">
         <v>1670.84147153657</v>
       </c>
       <c r="G73" t="n">
-        <v>1.87468911324186</v>
+        <v>1.87468913295083</v>
       </c>
       <c r="H73" t="n">
-        <v>8.47630692403212</v>
+        <v>8.47630687741453</v>
       </c>
       <c r="I73" t="n">
-        <v>454.209786973039</v>
+        <v>454.209786926025</v>
       </c>
       <c r="J73" t="n">
         <v>1670.84147153657</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="74">
@@ -6369,31 +6369,31 @@
         <v>22.8865176364712</v>
       </c>
       <c r="C74" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
       <c r="D74" t="n">
-        <v>432.746953251118</v>
+        <v>432.746953290138</v>
       </c>
       <c r="E74" t="n">
-        <v>1854.78530510666</v>
+        <v>1854.78530528243</v>
       </c>
       <c r="F74" t="n">
         <v>2000</v>
       </c>
       <c r="G74" t="n">
-        <v>145.214694893344</v>
+        <v>145.214694717575</v>
       </c>
       <c r="H74" t="n">
-        <v>25.2847552471223</v>
+        <v>25.2847552432837</v>
       </c>
       <c r="I74" t="n">
-        <v>458.03170849824</v>
+        <v>458.031708533422</v>
       </c>
       <c r="J74" t="n">
         <v>2000</v>
       </c>
       <c r="K74" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="75">
@@ -6404,31 +6404,31 @@
         <v>26.7654547629451</v>
       </c>
       <c r="C75" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
       <c r="D75" t="n">
-        <v>489.549259313156</v>
+        <v>489.549259361209</v>
       </c>
       <c r="E75" t="n">
-        <v>1854.78530510666</v>
+        <v>1854.78530528243</v>
       </c>
       <c r="F75" t="n">
         <v>2000</v>
       </c>
       <c r="G75" t="n">
-        <v>145.214694893344</v>
+        <v>145.214694717575</v>
       </c>
       <c r="H75" t="n">
-        <v>36.4157019668438</v>
+        <v>36.4157019640754</v>
       </c>
       <c r="I75" t="n">
-        <v>525.96496128</v>
+        <v>525.964961325285</v>
       </c>
       <c r="J75" t="n">
         <v>2000</v>
       </c>
       <c r="K75" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="76">
@@ -6439,31 +6439,31 @@
         <v>23.742438811814</v>
       </c>
       <c r="C76" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
       <c r="D76" t="n">
-        <v>445.280875555498</v>
+        <v>445.280875596511</v>
       </c>
       <c r="E76" t="n">
-        <v>1854.78530510666</v>
+        <v>1854.78530528243</v>
       </c>
       <c r="F76" t="n">
         <v>2000</v>
       </c>
       <c r="G76" t="n">
-        <v>145.214694893344</v>
+        <v>145.214694717575</v>
       </c>
       <c r="H76" t="n">
-        <v>41.8691470831967</v>
+        <v>41.8691470397897</v>
       </c>
       <c r="I76" t="n">
-        <v>487.150022638694</v>
+        <v>487.150022636301</v>
       </c>
       <c r="J76" t="n">
         <v>2000</v>
       </c>
       <c r="K76" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="77">
@@ -6474,31 +6474,31 @@
         <v>26.6055887887697</v>
       </c>
       <c r="C77" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
       <c r="D77" t="n">
-        <v>487.208216986885</v>
+        <v>487.208217034566</v>
       </c>
       <c r="E77" t="n">
-        <v>1854.78530510666</v>
+        <v>1854.78530528243</v>
       </c>
       <c r="F77" t="n">
         <v>2000</v>
       </c>
       <c r="G77" t="n">
-        <v>145.214694893344</v>
+        <v>145.214694717575</v>
       </c>
       <c r="H77" t="n">
-        <v>41.6450905961809</v>
+        <v>41.6450904704266</v>
       </c>
       <c r="I77" t="n">
-        <v>528.853307583066</v>
+        <v>528.853307504993</v>
       </c>
       <c r="J77" t="n">
         <v>2000</v>
       </c>
       <c r="K77" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="78">
@@ -6509,31 +6509,31 @@
         <v>27.5104125266935</v>
       </c>
       <c r="C78" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
       <c r="D78" t="n">
-        <v>512.291563786853</v>
+        <v>512.29156414789</v>
       </c>
       <c r="E78" t="n">
-        <v>2030.15141597623</v>
+        <v>2030.15141741735</v>
       </c>
       <c r="F78" t="n">
         <v>2100</v>
       </c>
       <c r="G78" t="n">
-        <v>69.8485840237688</v>
+        <v>69.8485825826474</v>
       </c>
       <c r="H78" t="n">
-        <v>35.7435325057965</v>
+        <v>35.743532255986</v>
       </c>
       <c r="I78" t="n">
-        <v>548.03509629265</v>
+        <v>548.035096403876</v>
       </c>
       <c r="J78" t="n">
         <v>2100</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="79">
@@ -6544,31 +6544,31 @@
         <v>29.6083132872694</v>
       </c>
       <c r="C79" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
       <c r="D79" t="n">
-        <v>543.012763230047</v>
+        <v>543.012763595969</v>
       </c>
       <c r="E79" t="n">
-        <v>2030.15141597623</v>
+        <v>2030.15141741735</v>
       </c>
       <c r="F79" t="n">
         <v>2100</v>
       </c>
       <c r="G79" t="n">
-        <v>69.8485840237688</v>
+        <v>69.8485825826474</v>
       </c>
       <c r="H79" t="n">
-        <v>26.070354669701</v>
+        <v>26.0703543260802</v>
       </c>
       <c r="I79" t="n">
-        <v>569.083117899748</v>
+        <v>569.083117922049</v>
       </c>
       <c r="J79" t="n">
         <v>2100</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="80">
@@ -6579,31 +6579,31 @@
         <v>25.2792692907187</v>
       </c>
       <c r="C80" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
       <c r="D80" t="n">
-        <v>479.619190704774</v>
+        <v>479.619191060614</v>
       </c>
       <c r="E80" t="n">
-        <v>2030.15141597623</v>
+        <v>2030.15141741735</v>
       </c>
       <c r="F80" t="n">
         <v>2100</v>
       </c>
       <c r="G80" t="n">
-        <v>69.8485840237688</v>
+        <v>69.8485825826474</v>
       </c>
       <c r="H80" t="n">
-        <v>12.6255570878945</v>
+        <v>12.6255566807092</v>
       </c>
       <c r="I80" t="n">
-        <v>492.244747792668</v>
+        <v>492.244747741323</v>
       </c>
       <c r="J80" t="n">
         <v>2100</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="81">
@@ -6614,31 +6614,31 @@
         <v>26.3451625511966</v>
       </c>
       <c r="C81" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
       <c r="D81" t="n">
-        <v>495.227898254557</v>
+        <v>495.22789861288</v>
       </c>
       <c r="E81" t="n">
-        <v>2030.15141597623</v>
+        <v>2030.15141741735</v>
       </c>
       <c r="F81" t="n">
         <v>2100</v>
       </c>
       <c r="G81" t="n">
-        <v>69.8485840237688</v>
+        <v>69.8485825826474</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.59086023962322</v>
+        <v>-4.5908606801271</v>
       </c>
       <c r="I81" t="n">
-        <v>490.637038014934</v>
+        <v>490.637037932753</v>
       </c>
       <c r="J81" t="n">
         <v>2100</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="82">
@@ -6649,31 +6649,31 @@
         <v>36.4266988798614</v>
       </c>
       <c r="C82" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
       <c r="D82" t="n">
-        <v>640.645929170218</v>
+        <v>640.645929491761</v>
       </c>
       <c r="E82" t="n">
-        <v>2471.15418656111</v>
+        <v>2471.15418783275</v>
       </c>
       <c r="F82" t="n">
         <v>2356.44230769231</v>
       </c>
       <c r="G82" t="n">
-        <v>-114.711878868807</v>
+        <v>-114.711880140439</v>
       </c>
       <c r="H82" t="n">
-        <v>-25.578897312852</v>
+        <v>-25.5788977564286</v>
       </c>
       <c r="I82" t="n">
-        <v>615.067031857366</v>
+        <v>615.067031735333</v>
       </c>
       <c r="J82" t="n">
         <v>2356.44230769231</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="83">
@@ -6684,31 +6684,31 @@
         <v>36.6392201947552</v>
       </c>
       <c r="C83" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
       <c r="D83" t="n">
-        <v>643.758044778103</v>
+        <v>643.758045100141</v>
       </c>
       <c r="E83" t="n">
-        <v>2471.15418656111</v>
+        <v>2471.15418783275</v>
       </c>
       <c r="F83" t="n">
         <v>2356.44230769231</v>
       </c>
       <c r="G83" t="n">
-        <v>-114.711878868807</v>
+        <v>-114.711880140439</v>
       </c>
       <c r="H83" t="n">
-        <v>-35.2137411038833</v>
+        <v>-35.2137414984215</v>
       </c>
       <c r="I83" t="n">
-        <v>608.54430367422</v>
+        <v>608.544303601719</v>
       </c>
       <c r="J83" t="n">
         <v>2356.44230769231</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="84">
@@ -6719,31 +6719,31 @@
         <v>34.1124802191808</v>
       </c>
       <c r="C84" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
       <c r="D84" t="n">
-        <v>606.7570177565</v>
+        <v>606.757018072653</v>
       </c>
       <c r="E84" t="n">
-        <v>2471.15418656111</v>
+        <v>2471.15418783275</v>
       </c>
       <c r="F84" t="n">
         <v>2356.44230769231</v>
       </c>
       <c r="G84" t="n">
-        <v>-114.711878868807</v>
+        <v>-114.711880140439</v>
       </c>
       <c r="H84" t="n">
-        <v>-33.4953916127173</v>
+        <v>-33.4953919061059</v>
       </c>
       <c r="I84" t="n">
-        <v>573.261626143782</v>
+        <v>573.261626166547</v>
       </c>
       <c r="J84" t="n">
         <v>2356.44230769231</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="85">
@@ -6754,31 +6754,31 @@
         <v>32.2848222684526</v>
       </c>
       <c r="C85" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
       <c r="D85" t="n">
-        <v>579.993194856294</v>
+        <v>579.993195168191</v>
       </c>
       <c r="E85" t="n">
-        <v>2471.15418656111</v>
+        <v>2471.15418783275</v>
       </c>
       <c r="F85" t="n">
         <v>2356.44230769231</v>
       </c>
       <c r="G85" t="n">
-        <v>-114.711878868807</v>
+        <v>-114.711880140439</v>
       </c>
       <c r="H85" t="n">
-        <v>-20.4238488393539</v>
+        <v>-20.4238489794817</v>
       </c>
       <c r="I85" t="n">
-        <v>559.56934601694</v>
+        <v>559.569346188709</v>
       </c>
       <c r="J85" t="n">
         <v>2356.44230769231</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="86">
@@ -6789,31 +6789,31 @@
         <v>29.0529285723371</v>
       </c>
       <c r="C86" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
       <c r="D86" t="n">
-        <v>517.391864764669</v>
+        <v>517.391864658731</v>
       </c>
       <c r="E86" t="n">
-        <v>2188.22692811224</v>
+        <v>2188.22692770736</v>
       </c>
       <c r="F86" t="n">
         <v>2252.37555077192</v>
       </c>
       <c r="G86" t="n">
-        <v>64.1486226596776</v>
+        <v>64.1486230645583</v>
       </c>
       <c r="H86" t="n">
-        <v>4.00088721620688</v>
+        <v>4.00088728145099</v>
       </c>
       <c r="I86" t="n">
-        <v>521.392751980875</v>
+        <v>521.392751940182</v>
       </c>
       <c r="J86" t="n">
         <v>2252.37555077192</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="87">
@@ -6824,31 +6824,31 @@
         <v>34.5333055575326</v>
       </c>
       <c r="C87" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
       <c r="D87" t="n">
-        <v>597.64530551363</v>
+        <v>597.645305420455</v>
       </c>
       <c r="E87" t="n">
-        <v>2188.22692811224</v>
+        <v>2188.22692770736</v>
       </c>
       <c r="F87" t="n">
         <v>2252.37555077192</v>
       </c>
       <c r="G87" t="n">
-        <v>64.1486226596776</v>
+        <v>64.1486230645583</v>
       </c>
       <c r="H87" t="n">
-        <v>18.5852890179162</v>
+        <v>18.5852891796996</v>
       </c>
       <c r="I87" t="n">
-        <v>616.230594531546</v>
+        <v>616.230594600155</v>
       </c>
       <c r="J87" t="n">
         <v>2252.37555077192</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="88">
@@ -6859,31 +6859,31 @@
         <v>28.5551821718171</v>
       </c>
       <c r="C88" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
       <c r="D88" t="n">
-        <v>510.102975447375</v>
+        <v>510.102975340278</v>
       </c>
       <c r="E88" t="n">
-        <v>2188.22692811224</v>
+        <v>2188.22692770736</v>
       </c>
       <c r="F88" t="n">
         <v>2252.37555077192</v>
       </c>
       <c r="G88" t="n">
-        <v>64.1486226596776</v>
+        <v>64.1486230645583</v>
       </c>
       <c r="H88" t="n">
-        <v>23.329356565774</v>
+        <v>23.3293567152641</v>
       </c>
       <c r="I88" t="n">
-        <v>533.432332013149</v>
+        <v>533.432332055542</v>
       </c>
       <c r="J88" t="n">
         <v>2252.37555077192</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="89">
@@ -6894,31 +6894,31 @@
         <v>32.1733602016653</v>
       </c>
       <c r="C89" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
       <c r="D89" t="n">
-        <v>563.086782386571</v>
+        <v>563.0867822879</v>
       </c>
       <c r="E89" t="n">
-        <v>2188.22692811224</v>
+        <v>2188.22692770736</v>
       </c>
       <c r="F89" t="n">
         <v>2252.37555077192</v>
       </c>
       <c r="G89" t="n">
-        <v>64.1486226596776</v>
+        <v>64.1486230645583</v>
       </c>
       <c r="H89" t="n">
-        <v>18.2330898597804</v>
+        <v>18.2330898881445</v>
       </c>
       <c r="I89" t="n">
-        <v>581.319872246351</v>
+        <v>581.319872176044</v>
       </c>
       <c r="J89" t="n">
         <v>2252.37555077192</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="90">
@@ -6929,31 +6929,31 @@
         <v>31.0258876982051</v>
       </c>
       <c r="C90" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
       <c r="D90" t="n">
-        <v>555.583346163295</v>
+        <v>555.58334631112</v>
       </c>
       <c r="E90" t="n">
-        <v>2381.83121316662</v>
+        <v>2381.83121378329</v>
       </c>
       <c r="F90" t="n">
         <v>2357.00684968791</v>
       </c>
       <c r="G90" t="n">
-        <v>-24.8243634787095</v>
+        <v>-24.8243640953756</v>
       </c>
       <c r="H90" t="n">
-        <v>3.29648889993531</v>
+        <v>3.29648869834082</v>
       </c>
       <c r="I90" t="n">
-        <v>558.87983506323</v>
+        <v>558.879835009461</v>
       </c>
       <c r="J90" t="n">
         <v>2357.00684968791</v>
       </c>
       <c r="K90" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="91">
@@ -6964,31 +6964,31 @@
         <v>36.8614010323591</v>
       </c>
       <c r="C91" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
       <c r="D91" t="n">
-        <v>641.037325856189</v>
+        <v>641.037326017604</v>
       </c>
       <c r="E91" t="n">
-        <v>2381.83121316662</v>
+        <v>2381.83121378329</v>
       </c>
       <c r="F91" t="n">
         <v>2357.00684968791</v>
       </c>
       <c r="G91" t="n">
-        <v>-24.8243634787095</v>
+        <v>-24.8243640953756</v>
       </c>
       <c r="H91" t="n">
-        <v>-6.47918339184778</v>
+        <v>-6.47918366645442</v>
       </c>
       <c r="I91" t="n">
-        <v>634.558142464341</v>
+        <v>634.558142351149</v>
       </c>
       <c r="J91" t="n">
         <v>2357.00684968791</v>
       </c>
       <c r="K91" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="92">
@@ -6999,31 +6999,31 @@
         <v>32.5631140019535</v>
       </c>
       <c r="C92" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
       <c r="D92" t="n">
-        <v>578.094151609504</v>
+        <v>578.094151760909</v>
       </c>
       <c r="E92" t="n">
-        <v>2381.83121316662</v>
+        <v>2381.83121378329</v>
       </c>
       <c r="F92" t="n">
         <v>2357.00684968791</v>
       </c>
       <c r="G92" t="n">
-        <v>-24.8243634787095</v>
+        <v>-24.8243640953756</v>
       </c>
       <c r="H92" t="n">
-        <v>-11.0939270155689</v>
+        <v>-11.0939272062412</v>
       </c>
       <c r="I92" t="n">
-        <v>567.000224593935</v>
+        <v>567.000224554668</v>
       </c>
       <c r="J92" t="n">
         <v>2357.00684968791</v>
       </c>
       <c r="K92" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="93">
@@ -7034,31 +7034,31 @@
         <v>34.5449954429963</v>
       </c>
       <c r="C93" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
       <c r="D93" t="n">
-        <v>607.116389537635</v>
+        <v>607.116389693655</v>
       </c>
       <c r="E93" t="n">
-        <v>2381.83121316662</v>
+        <v>2381.83121378329</v>
       </c>
       <c r="F93" t="n">
         <v>2357.00684968791</v>
       </c>
       <c r="G93" t="n">
-        <v>-24.8243634787095</v>
+        <v>-24.8243640953756</v>
       </c>
       <c r="H93" t="n">
-        <v>-10.5477419712279</v>
+        <v>-10.5477419210194</v>
       </c>
       <c r="I93" t="n">
-        <v>596.568647566407</v>
+        <v>596.568647772636</v>
       </c>
       <c r="J93" t="n">
         <v>2357.00684968791</v>
       </c>
       <c r="K93" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="94">
@@ -7066,34 +7066,34 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>34.8365640886945</v>
+        <v>34.8365640318403</v>
       </c>
       <c r="C94" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
       <c r="D94" t="n">
-        <v>607.297470374948</v>
+        <v>607.297469588803</v>
       </c>
       <c r="E94" t="n">
-        <v>2520.53385109348</v>
+        <v>2520.53384790894</v>
       </c>
       <c r="F94" t="n">
         <v>2521.14623605159</v>
       </c>
       <c r="G94" t="n">
-        <v>0.612384958110397</v>
+        <v>0.612388142647433</v>
       </c>
       <c r="H94" t="n">
-        <v>-4.84062825882492</v>
+        <v>-4.84062781078922</v>
       </c>
       <c r="I94" t="n">
-        <v>602.456842116123</v>
+        <v>602.456841778014</v>
       </c>
       <c r="J94" t="n">
         <v>2521.14623605159</v>
       </c>
       <c r="K94" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="95">
@@ -7101,34 +7101,34 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>37.1433012120465</v>
+        <v>37.1433011512908</v>
       </c>
       <c r="C95" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
       <c r="D95" t="n">
-        <v>641.076823793963</v>
+        <v>641.076822956058</v>
       </c>
       <c r="E95" t="n">
-        <v>2520.53385109348</v>
+        <v>2520.53384790894</v>
       </c>
       <c r="F95" t="n">
         <v>2521.14623605159</v>
       </c>
       <c r="G95" t="n">
-        <v>0.612384958110397</v>
+        <v>0.612388142647433</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.560292974522694</v>
+        <v>-0.560292228116561</v>
       </c>
       <c r="I95" t="n">
-        <v>640.516530819441</v>
+        <v>640.516530727942</v>
       </c>
       <c r="J95" t="n">
         <v>2521.14623605159</v>
       </c>
       <c r="K95" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="96">
@@ -7136,34 +7136,34 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>36.1297566732804</v>
+        <v>36.129756615845</v>
       </c>
       <c r="C96" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
       <c r="D96" t="n">
-        <v>626.23469946419</v>
+        <v>626.234698672547</v>
       </c>
       <c r="E96" t="n">
-        <v>2520.53385109348</v>
+        <v>2520.53384790894</v>
       </c>
       <c r="F96" t="n">
         <v>2521.14623605159</v>
       </c>
       <c r="G96" t="n">
-        <v>0.612384958110397</v>
+        <v>0.612388142647433</v>
       </c>
       <c r="H96" t="n">
-        <v>2.29326388167879</v>
+        <v>2.29326482699855</v>
       </c>
       <c r="I96" t="n">
-        <v>628.527963345869</v>
+        <v>628.527963499545</v>
       </c>
       <c r="J96" t="n">
         <v>2521.14623605159</v>
       </c>
       <c r="K96" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
     <row r="97">
@@ -7171,34 +7171,34 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>37.4743655487392</v>
+        <v>37.4743654926469</v>
       </c>
       <c r="C97" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
       <c r="D97" t="n">
-        <v>645.924857460377</v>
+        <v>645.924856691533</v>
       </c>
       <c r="E97" t="n">
-        <v>2520.53385109348</v>
+        <v>2520.53384790894</v>
       </c>
       <c r="F97" t="n">
         <v>2521.14623605159</v>
       </c>
       <c r="G97" t="n">
-        <v>0.612384958110397</v>
+        <v>0.612388142647433</v>
       </c>
       <c r="H97" t="n">
-        <v>3.72004230977954</v>
+        <v>3.7200433545561</v>
       </c>
       <c r="I97" t="n">
-        <v>649.644899770156</v>
+        <v>649.644900046089</v>
       </c>
       <c r="J97" t="n">
         <v>2521.14623605159</v>
       </c>
       <c r="K97" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.00000000000136424205265939</v>
       </c>
     </row>
   </sheetData>
@@ -7231,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>255.982795813224</v>
+        <v>255.982795813169</v>
       </c>
       <c r="C2" t="n">
         <v>9.23693404109287</v>
       </c>
       <c r="D2" t="n">
-        <v>14.2986279212355</v>
+        <v>14.2986295661159</v>
       </c>
     </row>
     <row r="3">
@@ -7245,13 +7245,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>261.312073564617</v>
+        <v>261.312073565083</v>
       </c>
       <c r="C3" t="n">
         <v>9.61533075382236</v>
       </c>
       <c r="D3" t="n">
-        <v>14.2986279212355</v>
+        <v>14.2986295661159</v>
       </c>
     </row>
     <row r="4">
@@ -7259,13 +7259,13 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>251.389182769784</v>
+        <v>251.389182768018</v>
       </c>
       <c r="C4" t="n">
         <v>8.96665067485753</v>
       </c>
       <c r="D4" t="n">
-        <v>14.2986279212355</v>
+        <v>14.2986295661159</v>
       </c>
     </row>
     <row r="5">
@@ -7273,13 +7273,13 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>277.172992867541</v>
+        <v>277.172992868896</v>
       </c>
       <c r="C5" t="n">
         <v>10.7707921444785</v>
       </c>
       <c r="D5" t="n">
-        <v>14.2986279212355</v>
+        <v>14.2986295661159</v>
       </c>
     </row>
     <row r="6">
@@ -7287,13 +7287,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>261.997595884093</v>
+        <v>261.99759589105</v>
       </c>
       <c r="C6" t="n">
         <v>9.39376000248317</v>
       </c>
       <c r="D6" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
     </row>
     <row r="7">
@@ -7301,13 +7301,13 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>266.777352591268</v>
+        <v>266.777352595373</v>
       </c>
       <c r="C7" t="n">
         <v>9.77858118766171</v>
       </c>
       <c r="D7" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
     </row>
     <row r="8">
@@ -7315,13 +7315,13 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>256.253508495529</v>
+        <v>256.253508492043</v>
       </c>
       <c r="C8" t="n">
         <v>9.11888772735565</v>
       </c>
       <c r="D8" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
     </row>
     <row r="9">
@@ -7329,13 +7329,13 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>282.250119866688</v>
+        <v>282.250119859112</v>
       </c>
       <c r="C9" t="n">
         <v>10.9536601638319</v>
       </c>
       <c r="D9" t="n">
-        <v>88.2130687340323</v>
+        <v>88.2130685505051</v>
       </c>
     </row>
     <row r="10">
@@ -7343,13 +7343,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>268.283503175323</v>
+        <v>268.283503179471</v>
       </c>
       <c r="C10" t="n">
         <v>9.99617052517854</v>
       </c>
       <c r="D10" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
     </row>
     <row r="11">
@@ -7357,13 +7357,13 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>270.32648136992</v>
+        <v>270.326481369067</v>
       </c>
       <c r="C11" t="n">
         <v>10.3276944445079</v>
       </c>
       <c r="D11" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
     </row>
     <row r="12">
@@ -7371,13 +7371,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>237.819162619841</v>
+        <v>237.819162613695</v>
       </c>
       <c r="C12" t="n">
         <v>8.43179753569241</v>
       </c>
       <c r="D12" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
     </row>
     <row r="13">
@@ -7385,13 +7385,13 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>262.440619972926</v>
+        <v>262.440619975776</v>
       </c>
       <c r="C13" t="n">
         <v>10.5690946367562</v>
       </c>
       <c r="D13" t="n">
-        <v>100.040266591781</v>
+        <v>100.040266406729</v>
       </c>
     </row>
     <row r="14">
@@ -7399,13 +7399,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>240.042920815036</v>
+        <v>240.042920763081</v>
       </c>
       <c r="C14" t="n">
         <v>9.78700271451556</v>
       </c>
       <c r="D14" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
     </row>
     <row r="15">
@@ -7413,13 +7413,13 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>228.203929921215</v>
+        <v>228.203929893296</v>
       </c>
       <c r="C15" t="n">
         <v>9.43061325992536</v>
       </c>
       <c r="D15" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
     </row>
     <row r="16">
@@ -7427,13 +7427,13 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>207.564875063179</v>
+        <v>207.564875073531</v>
       </c>
       <c r="C16" t="n">
         <v>8.33745714440349</v>
       </c>
       <c r="D16" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
     </row>
     <row r="17">
@@ -7441,13 +7441,13 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>220.027414307894</v>
+        <v>220.027414377415</v>
       </c>
       <c r="C17" t="n">
         <v>9.36893046970783</v>
       </c>
       <c r="D17" t="n">
-        <v>70.461886495382</v>
+        <v>70.4618863101432</v>
       </c>
     </row>
     <row r="18">
@@ -7455,13 +7455,13 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>216.399251709625</v>
+        <v>216.399251627495</v>
       </c>
       <c r="C18" t="n">
         <v>9.74751579800055</v>
       </c>
       <c r="D18" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
     </row>
     <row r="19">
@@ -7469,13 +7469,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>215.005687479662</v>
+        <v>215.005687459056</v>
       </c>
       <c r="C19" t="n">
         <v>9.67083034417807</v>
       </c>
       <c r="D19" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
     </row>
     <row r="20">
@@ -7483,13 +7483,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>201.796990968055</v>
+        <v>201.796990996016</v>
       </c>
       <c r="C20" t="n">
         <v>8.76118531638173</v>
       </c>
       <c r="D20" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
     </row>
     <row r="21">
@@ -7497,13 +7497,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>247.21739258822</v>
+        <v>247.217392662996</v>
       </c>
       <c r="C21" t="n">
         <v>11.8291026747245</v>
       </c>
       <c r="D21" t="n">
-        <v>-37.4126310950619</v>
+        <v>-37.4126312747098</v>
       </c>
     </row>
     <row r="22">
@@ -7511,13 +7511,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>228.833487201618</v>
+        <v>228.833487175413</v>
       </c>
       <c r="C22" t="n">
         <v>10.8405558524574</v>
       </c>
       <c r="D22" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
     </row>
     <row r="23">
@@ -7525,13 +7525,13 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>222.985308223356</v>
+        <v>222.985308218301</v>
       </c>
       <c r="C23" t="n">
         <v>10.4064097033053</v>
       </c>
       <c r="D23" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
     </row>
     <row r="24">
@@ -7539,13 +7539,13 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>206.943153695471</v>
+        <v>206.94315370351</v>
       </c>
       <c r="C24" t="n">
         <v>9.30124144311374</v>
       </c>
       <c r="D24" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
     </row>
     <row r="25">
@@ -7553,13 +7553,13 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>244.492601117224</v>
+        <v>244.492601140446</v>
       </c>
       <c r="C25" t="n">
         <v>11.8808644507488</v>
       </c>
       <c r="D25" t="n">
-        <v>-98.0031028338607</v>
+        <v>-98.0031030206923</v>
       </c>
     </row>
     <row r="26">
@@ -7567,13 +7567,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>235.960206159004</v>
+        <v>235.960206156979</v>
       </c>
       <c r="C26" t="n">
         <v>11.4067396261152</v>
       </c>
       <c r="D26" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
     </row>
     <row r="27">
@@ -7581,13 +7581,13 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>205.959297258621</v>
+        <v>205.959297254804</v>
       </c>
       <c r="C27" t="n">
         <v>9.28905311211552</v>
       </c>
       <c r="D27" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
     </row>
     <row r="28">
@@ -7595,13 +7595,13 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>204.503840137178</v>
+        <v>204.503840136311</v>
       </c>
       <c r="C28" t="n">
         <v>9.01117566522454</v>
       </c>
       <c r="D28" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
     </row>
     <row r="29">
@@ -7609,13 +7609,13 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>230.871974264513</v>
+        <v>230.871974271224</v>
       </c>
       <c r="C29" t="n">
         <v>10.5238126035059</v>
       </c>
       <c r="D29" t="n">
-        <v>-110.61222949444</v>
+        <v>-110.612229686909</v>
       </c>
     </row>
     <row r="30">
@@ -7623,13 +7623,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>257.524477931073</v>
+        <v>257.524477958973</v>
       </c>
       <c r="C30" t="n">
         <v>11.9127471155729</v>
       </c>
       <c r="D30" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
     </row>
     <row r="31">
@@ -7637,13 +7637,13 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>246.737105927901</v>
+        <v>246.737105945096</v>
       </c>
       <c r="C31" t="n">
         <v>10.8348612881606</v>
       </c>
       <c r="D31" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
     </row>
     <row r="32">
@@ -7651,13 +7651,13 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>224.469613637607</v>
+        <v>224.469613629695</v>
       </c>
       <c r="C32" t="n">
         <v>9.02929647186484</v>
       </c>
       <c r="D32" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
     </row>
     <row r="33">
@@ -7665,13 +7665,13 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>255.09342047595</v>
+        <v>255.093420438765</v>
       </c>
       <c r="C33" t="n">
         <v>10.8918722375126</v>
       </c>
       <c r="D33" t="n">
-        <v>-104.380177943472</v>
+        <v>-104.380178130821</v>
       </c>
     </row>
     <row r="34">
@@ -7679,13 +7679,13 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>253.725725333807</v>
+        <v>253.725725396531</v>
       </c>
       <c r="C34" t="n">
         <v>10.2441206518659</v>
       </c>
       <c r="D34" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
     </row>
     <row r="35">
@@ -7693,13 +7693,13 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>258.11537461217</v>
+        <v>258.115374631454</v>
       </c>
       <c r="C35" t="n">
         <v>10.4852423350932</v>
       </c>
       <c r="D35" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
     </row>
     <row r="36">
@@ -7707,13 +7707,13 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>260.768276989571</v>
+        <v>260.768276967719</v>
       </c>
       <c r="C36" t="n">
         <v>10.721518519552</v>
       </c>
       <c r="D36" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
     </row>
     <row r="37">
@@ -7721,13 +7721,13 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>264.994579151152</v>
+        <v>264.994579090995</v>
       </c>
       <c r="C37" t="n">
         <v>11.1789937404245</v>
       </c>
       <c r="D37" t="n">
-        <v>-33.5523590167572</v>
+        <v>-33.5523592097836</v>
       </c>
     </row>
     <row r="38">
@@ -7735,13 +7735,13 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>267.377896311235</v>
+        <v>267.377896328095</v>
       </c>
       <c r="C38" t="n">
         <v>11.3312759206842</v>
       </c>
       <c r="D38" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
     </row>
     <row r="39">
@@ -7749,13 +7749,13 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>276.150262285289</v>
+        <v>276.150262281898</v>
       </c>
       <c r="C39" t="n">
         <v>12.1178813133434</v>
       </c>
       <c r="D39" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
     </row>
     <row r="40">
@@ -7763,13 +7763,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>250.502228078443</v>
+        <v>250.502228064076</v>
       </c>
       <c r="C40" t="n">
         <v>10.4589062836713</v>
       </c>
       <c r="D40" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
     </row>
     <row r="41">
@@ -7777,13 +7777,13 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>297.11026728378</v>
+        <v>297.110267284679</v>
       </c>
       <c r="C41" t="n">
         <v>13.6391137687502</v>
       </c>
       <c r="D41" t="n">
-        <v>20.7966495088722</v>
+        <v>20.7966493159365</v>
       </c>
     </row>
     <row r="42">
@@ -7791,13 +7791,13 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>267.848933641568</v>
+        <v>267.848933621099</v>
       </c>
       <c r="C42" t="n">
         <v>11.6428691387851</v>
       </c>
       <c r="D42" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
     </row>
     <row r="43">
@@ -7805,13 +7805,13 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>277.772921036527</v>
+        <v>277.772921033725</v>
       </c>
       <c r="C43" t="n">
         <v>12.3919304064259</v>
       </c>
       <c r="D43" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
     </row>
     <row r="44">
@@ -7819,13 +7819,13 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>264.82905543948</v>
+        <v>264.829055444194</v>
       </c>
       <c r="C44" t="n">
         <v>11.7483984681507</v>
       </c>
       <c r="D44" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
     </row>
     <row r="45">
@@ -7833,13 +7833,13 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>332.63700750994</v>
+        <v>332.637007528499</v>
       </c>
       <c r="C45" t="n">
         <v>16.7882921587443</v>
       </c>
       <c r="D45" t="n">
-        <v>2.32545286218942</v>
+        <v>2.32545265780232</v>
       </c>
     </row>
     <row r="46">
@@ -7847,13 +7847,13 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>263.346385599537</v>
+        <v>263.346385557722</v>
       </c>
       <c r="C46" t="n">
         <v>12.7515959096748</v>
       </c>
       <c r="D46" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
     </row>
     <row r="47">
@@ -7861,13 +7861,13 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>283.954241065729</v>
+        <v>283.954241041558</v>
       </c>
       <c r="C47" t="n">
         <v>14.4607563865404</v>
       </c>
       <c r="D47" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
     </row>
     <row r="48">
@@ -7875,13 +7875,13 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>261.424102537725</v>
+        <v>261.424102542157</v>
       </c>
       <c r="C48" t="n">
         <v>12.94756273816</v>
       </c>
       <c r="D48" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
     </row>
     <row r="49">
@@ -7889,13 +7889,13 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>306.184249099894</v>
+        <v>306.18424916145</v>
       </c>
       <c r="C49" t="n">
         <v>15.7529825985791</v>
       </c>
       <c r="D49" t="n">
-        <v>-19.3022213907495</v>
+        <v>-19.3022216068373</v>
       </c>
     </row>
     <row r="50">
@@ -7903,13 +7903,13 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>273.346214898814</v>
+        <v>273.346214862</v>
       </c>
       <c r="C50" t="n">
         <v>13.3986549446632</v>
       </c>
       <c r="D50" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
     </row>
     <row r="51">
@@ -7917,13 +7917,13 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>332.745041336489</v>
+        <v>332.745041348223</v>
       </c>
       <c r="C51" t="n">
         <v>16.7879730089583</v>
       </c>
       <c r="D51" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
     </row>
     <row r="52">
@@ -7931,13 +7931,13 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>293.483731661643</v>
+        <v>293.48373167751</v>
       </c>
       <c r="C52" t="n">
         <v>13.3007279982884</v>
       </c>
       <c r="D52" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
     </row>
     <row r="53">
@@ -7945,13 +7945,13 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>367.019261470462</v>
+        <v>367.019261479676</v>
       </c>
       <c r="C53" t="n">
         <v>17.3769729695861</v>
       </c>
       <c r="D53" t="n">
-        <v>-96.4120000356888</v>
+        <v>-96.4120002595582</v>
       </c>
     </row>
     <row r="54">
@@ -7959,13 +7959,13 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>369.272800482928</v>
+        <v>369.272800609177</v>
       </c>
       <c r="C54" t="n">
         <v>16.0192758607371</v>
       </c>
       <c r="D54" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
     </row>
     <row r="55">
@@ -7973,13 +7973,13 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>406.483215218855</v>
+        <v>406.48321528131</v>
       </c>
       <c r="C55" t="n">
         <v>18.0480441521233</v>
       </c>
       <c r="D55" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
     </row>
     <row r="56">
@@ -7987,13 +7987,13 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>358.500851078175</v>
+        <v>358.500851040648</v>
       </c>
       <c r="C56" t="n">
         <v>14.8314652467803</v>
       </c>
       <c r="D56" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
     </row>
     <row r="57">
@@ -8001,13 +8001,13 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>366.923795034997</v>
+        <v>366.92379488382</v>
       </c>
       <c r="C57" t="n">
         <v>16.0390422807548</v>
       </c>
       <c r="D57" t="n">
-        <v>-17.2344047407294</v>
+        <v>-17.2344049761298</v>
       </c>
     </row>
     <row r="58">
@@ -8015,13 +8015,13 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>129.656037155289</v>
+        <v>129.656037191797</v>
       </c>
       <c r="C58" t="n">
         <v>0.0977424856544318</v>
       </c>
       <c r="D58" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
     </row>
     <row r="59">
@@ -8029,13 +8029,13 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>317.253237612197</v>
+        <v>317.253237599077</v>
       </c>
       <c r="C59" t="n">
         <v>14.0447704192465</v>
       </c>
       <c r="D59" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
     </row>
     <row r="60">
@@ -8043,13 +8043,13 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>348.969500973955</v>
+        <v>348.969500944586</v>
       </c>
       <c r="C60" t="n">
         <v>17.2785456875479</v>
       </c>
       <c r="D60" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
     </row>
     <row r="61">
@@ -8057,13 +8057,13 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>339.381695383643</v>
+        <v>339.381695389626</v>
       </c>
       <c r="C61" t="n">
         <v>17.6233363262596</v>
       </c>
       <c r="D61" t="n">
-        <v>157.700585745164</v>
+        <v>157.700585500277</v>
       </c>
     </row>
     <row r="62">
@@ -8071,13 +8071,13 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>318.814114980929</v>
+        <v>318.814114804645</v>
       </c>
       <c r="C62" t="n">
         <v>17.868151976636</v>
       </c>
       <c r="D62" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
     </row>
     <row r="63">
@@ -8085,13 +8085,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>330.992639338383</v>
+        <v>330.992639271651</v>
       </c>
       <c r="C63" t="n">
         <v>19.0161167301949</v>
       </c>
       <c r="D63" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
     </row>
     <row r="64">
@@ -8099,13 +8099,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>344.407915658947</v>
+        <v>344.407915714534</v>
       </c>
       <c r="C64" t="n">
         <v>19.6337210138089</v>
       </c>
       <c r="D64" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
     </row>
     <row r="65">
@@ -8113,13 +8113,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>338.655670631493</v>
+        <v>338.655670818923</v>
       </c>
       <c r="C65" t="n">
         <v>18.3275901782376</v>
       </c>
       <c r="D65" t="n">
-        <v>24.5203428084815</v>
+        <v>24.5203426006074</v>
       </c>
     </row>
     <row r="66">
@@ -8127,13 +8127,13 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>342.987325054088</v>
+        <v>342.987325008007</v>
       </c>
       <c r="C66" t="n">
         <v>18.0671285639402</v>
       </c>
       <c r="D66" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
     </row>
     <row r="67">
@@ -8141,13 +8141,13 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>397.289955469336</v>
+        <v>397.289955505723</v>
       </c>
       <c r="C67" t="n">
         <v>20.8122714076788</v>
       </c>
       <c r="D67" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
     </row>
     <row r="68">
@@ -8155,13 +8155,13 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>385.30111753914</v>
+        <v>385.301117575954</v>
       </c>
       <c r="C68" t="n">
         <v>19.5955177898177</v>
       </c>
       <c r="D68" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
     </row>
     <row r="69">
@@ -8169,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>418.178375611118</v>
+        <v>418.178375583999</v>
       </c>
       <c r="C69" t="n">
         <v>22.00763704929</v>
       </c>
       <c r="D69" t="n">
-        <v>-155.696691887444</v>
+        <v>-155.696692155404</v>
       </c>
     </row>
     <row r="70">
@@ -8183,13 +8183,13 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>379.900935686686</v>
+        <v>379.900935778683</v>
       </c>
       <c r="C70" t="n">
         <v>19.4336483530636</v>
       </c>
       <c r="D70" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
     </row>
     <row r="71">
@@ -8197,13 +8197,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>439.586918222457</v>
+        <v>439.586918228478</v>
       </c>
       <c r="C71" t="n">
         <v>23.7715703226929</v>
       </c>
       <c r="D71" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
     </row>
     <row r="72">
@@ -8211,13 +8211,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>397.143830654391</v>
+        <v>397.143830603387</v>
       </c>
       <c r="C72" t="n">
         <v>20.6653025217431</v>
       </c>
       <c r="D72" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
     </row>
     <row r="73">
@@ -8225,13 +8225,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>454.209786973039</v>
+        <v>454.209786926025</v>
       </c>
       <c r="C73" t="n">
         <v>23.8843839125212</v>
       </c>
       <c r="D73" t="n">
-        <v>-27.3568853263143</v>
+        <v>-27.3568856074014</v>
       </c>
     </row>
     <row r="74">
@@ -8239,13 +8239,13 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>458.03170849824</v>
+        <v>458.031708533422</v>
       </c>
       <c r="C74" t="n">
         <v>22.8865176364712</v>
       </c>
       <c r="D74" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
     </row>
     <row r="75">
@@ -8253,13 +8253,13 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>525.96496128</v>
+        <v>525.964961325285</v>
       </c>
       <c r="C75" t="n">
         <v>26.7654547629451</v>
       </c>
       <c r="D75" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
     </row>
     <row r="76">
@@ -8267,13 +8267,13 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>487.150022638694</v>
+        <v>487.150022636301</v>
       </c>
       <c r="C76" t="n">
         <v>23.742438811814</v>
       </c>
       <c r="D76" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
     </row>
     <row r="77">
@@ -8281,13 +8281,13 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>528.853307583066</v>
+        <v>528.853307504993</v>
       </c>
       <c r="C77" t="n">
         <v>26.6055887887697</v>
       </c>
       <c r="D77" t="n">
-        <v>-6.7668931062467</v>
+        <v>-6.76689340426969</v>
       </c>
     </row>
     <row r="78">
@@ -8295,13 +8295,13 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>548.03509629265</v>
+        <v>548.035096403876</v>
       </c>
       <c r="C78" t="n">
         <v>27.5104125266935</v>
       </c>
       <c r="D78" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
     </row>
     <row r="79">
@@ -8309,13 +8309,13 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>569.083117899748</v>
+        <v>569.083117922049</v>
       </c>
       <c r="C79" t="n">
         <v>29.6083132872694</v>
       </c>
       <c r="D79" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
     </row>
     <row r="80">
@@ -8323,13 +8323,13 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>492.244747792668</v>
+        <v>492.244747741323</v>
       </c>
       <c r="C80" t="n">
         <v>25.2792692907187</v>
       </c>
       <c r="D80" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
     </row>
     <row r="81">
@@ -8337,13 +8337,13 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>490.637038014934</v>
+        <v>490.637037932753</v>
       </c>
       <c r="C81" t="n">
         <v>26.3451625511966</v>
       </c>
       <c r="D81" t="n">
-        <v>143.077146614341</v>
+        <v>143.077146287802</v>
       </c>
     </row>
     <row r="82">
@@ -8351,13 +8351,13 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>615.067031857366</v>
+        <v>615.067031735333</v>
       </c>
       <c r="C82" t="n">
         <v>36.4266988798614</v>
       </c>
       <c r="D82" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
     </row>
     <row r="83">
@@ -8365,13 +8365,13 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>608.54430367422</v>
+        <v>608.544303601719</v>
       </c>
       <c r="C83" t="n">
         <v>36.6392201947552</v>
       </c>
       <c r="D83" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
     </row>
     <row r="84">
@@ -8379,13 +8379,13 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>573.261626143782</v>
+        <v>573.261626166547</v>
       </c>
       <c r="C84" t="n">
         <v>34.1124802191808</v>
       </c>
       <c r="D84" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
     </row>
     <row r="85">
@@ -8393,13 +8393,13 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>559.56934601694</v>
+        <v>559.569346188709</v>
       </c>
       <c r="C85" t="n">
         <v>32.2848222684526</v>
       </c>
       <c r="D85" t="n">
-        <v>115.044260046445</v>
+        <v>115.044259699544</v>
       </c>
     </row>
     <row r="86">
@@ -8407,13 +8407,13 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>521.392751980875</v>
+        <v>521.392751940182</v>
       </c>
       <c r="C86" t="n">
         <v>29.0529285723371</v>
       </c>
       <c r="D86" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
     </row>
     <row r="87">
@@ -8421,13 +8421,13 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>616.230594531546</v>
+        <v>616.230594600155</v>
       </c>
       <c r="C87" t="n">
         <v>34.5333055575326</v>
       </c>
       <c r="D87" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
     </row>
     <row r="88">
@@ -8435,13 +8435,13 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>533.432332013149</v>
+        <v>533.432332055542</v>
       </c>
       <c r="C88" t="n">
         <v>28.5551821718171</v>
       </c>
       <c r="D88" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
     </row>
     <row r="89">
@@ -8449,13 +8449,13 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>581.319872246351</v>
+        <v>581.319872176044</v>
       </c>
       <c r="C89" t="n">
         <v>32.1733602016653</v>
       </c>
       <c r="D89" t="n">
-        <v>-78.3713225440242</v>
+        <v>-78.3713229624659</v>
       </c>
     </row>
     <row r="90">
@@ -8463,13 +8463,13 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>558.87983506323</v>
+        <v>558.879835009461</v>
       </c>
       <c r="C90" t="n">
         <v>31.0258876982051</v>
       </c>
       <c r="D90" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
     </row>
     <row r="91">
@@ -8477,13 +8477,13 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>634.558142464341</v>
+        <v>634.558142351149</v>
       </c>
       <c r="C91" t="n">
         <v>36.8614010323591</v>
       </c>
       <c r="D91" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
     </row>
     <row r="92">
@@ -8491,13 +8491,13 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>567.000224593935</v>
+        <v>567.000224554668</v>
       </c>
       <c r="C92" t="n">
         <v>32.5631140019535</v>
       </c>
       <c r="D92" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
     </row>
     <row r="93">
@@ -8505,13 +8505,13 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>596.568647566407</v>
+        <v>596.568647772636</v>
       </c>
       <c r="C93" t="n">
         <v>34.5449954429963</v>
       </c>
       <c r="D93" t="n">
-        <v>39.3924335198717</v>
+        <v>39.3924331367075</v>
       </c>
     </row>
     <row r="94">
@@ -8519,13 +8519,13 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>602.456842116123</v>
+        <v>602.456841778014</v>
       </c>
       <c r="C94" t="n">
-        <v>34.8365640886945</v>
+        <v>34.8365640318403</v>
       </c>
       <c r="D94" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
     </row>
     <row r="95">
@@ -8533,13 +8533,13 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>640.516530819441</v>
+        <v>640.516530727942</v>
       </c>
       <c r="C95" t="n">
-        <v>37.1433012120465</v>
+        <v>37.1433011512908</v>
       </c>
       <c r="D95" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
     </row>
     <row r="96">
@@ -8547,13 +8547,13 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>628.527963345869</v>
+        <v>628.527963499545</v>
       </c>
       <c r="C96" t="n">
-        <v>36.1297566732804</v>
+        <v>36.129756615845</v>
       </c>
       <c r="D96" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
     </row>
     <row r="97">
@@ -8561,13 +8561,13 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>649.644899770156</v>
+        <v>649.644900046089</v>
       </c>
       <c r="C97" t="n">
-        <v>37.4743655487392</v>
+        <v>37.4743654926469</v>
       </c>
       <c r="D97" t="n">
-        <v>-12.3809530163262</v>
+        <v>-12.3809534243633</v>
       </c>
     </row>
     <row r="98">
@@ -8575,13 +8575,13 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>656.659782073545</v>
+        <v>656.659781662923</v>
       </c>
       <c r="C98" t="n">
-        <v>38.1611757374119</v>
+        <v>38.1611756838552</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.95069103672792</v>
+        <v>-0.950690184130915</v>
       </c>
     </row>
     <row r="99">
@@ -8589,13 +8589,13 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>678.89869479132</v>
+        <v>678.898694362334</v>
       </c>
       <c r="C99" t="n">
-        <v>39.6787472825931</v>
+        <v>39.678747228501</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.900269710784061</v>
+        <v>-0.900268904022613</v>
       </c>
     </row>
     <row r="100">
@@ -8603,13 +8603,13 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>654.508205519239</v>
+        <v>654.508205065739</v>
       </c>
       <c r="C100" t="n">
-        <v>38.0109851341196</v>
+        <v>38.0109850805385</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.799427058896341</v>
+        <v>-0.799426343806009</v>
       </c>
     </row>
     <row r="101">
@@ -8617,13 +8617,13 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>688.284233817555</v>
+        <v>688.284233375457</v>
       </c>
       <c r="C101" t="n">
-        <v>40.3142322517522</v>
+        <v>40.3142322014632</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.648163081064762</v>
+        <v>-0.648162503481103</v>
       </c>
     </row>
     <row r="102">
@@ -8631,13 +8631,13 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>671.159885431994</v>
+        <v>671.15988483473</v>
       </c>
       <c r="C102" t="n">
-        <v>39.1404877580255</v>
+        <v>39.1404877011668</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.446477777289323</v>
+        <v>-0.446477383047895</v>
       </c>
     </row>
     <row r="103">
@@ -8645,13 +8645,13 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>709.370205950205</v>
+        <v>709.3702054116</v>
       </c>
       <c r="C103" t="n">
-        <v>41.7464633915038</v>
+        <v>41.7464633411794</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.291408246820199</v>
+        <v>-0.291407993122925</v>
       </c>
     </row>
     <row r="104">
@@ -8659,13 +8659,13 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>684.312630833177</v>
+        <v>684.312630263071</v>
       </c>
       <c r="C104" t="n">
-        <v>40.0329828549618</v>
+        <v>40.0329828048053</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.18295448965739</v>
+        <v>-0.182954333706193</v>
       </c>
     </row>
     <row r="105">
@@ -8673,13 +8673,13 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>723.973417815487</v>
+        <v>723.973417280874</v>
       </c>
       <c r="C105" t="n">
-        <v>42.7400195970638</v>
+        <v>42.7400195500505</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.121116505800895</v>
+        <v>-0.121116404797699</v>
       </c>
     </row>
     <row r="106">
@@ -8687,13 +8687,13 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>698.796538060153</v>
+        <v>698.796537367731</v>
       </c>
       <c r="C106" t="n">
-        <v>41.020403052843</v>
+        <v>41.02040299558</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.105894295250715</v>
+        <v>-0.105894206397443</v>
       </c>
     </row>
     <row r="107">
@@ -8701,13 +8701,13 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>732.954568270457</v>
+        <v>732.954567694286</v>
       </c>
       <c r="C107" t="n">
-        <v>43.3526643354822</v>
+        <v>43.3526642860518</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.0903613713201528</v>
+        <v>-0.0903612951560823</v>
       </c>
     </row>
     <row r="108">
@@ -8715,13 +8715,13 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>715.991722116477</v>
+        <v>715.991721566619</v>
       </c>
       <c r="C108" t="n">
-        <v>42.1939573858609</v>
+        <v>42.193957338688</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.0745177340092083</v>
+        <v>-0.0745176710736161</v>
       </c>
     </row>
     <row r="109">
@@ -8729,13 +8729,13 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>753.386005871008</v>
+        <v>753.386005335841</v>
       </c>
       <c r="C109" t="n">
-        <v>44.7472037563392</v>
+        <v>44.7472037100511</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.0583633833178814</v>
+        <v>-0.0583633341500447</v>
       </c>
     </row>
     <row r="110">
@@ -8743,13 +8743,13 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>739.55744920148</v>
+        <v>739.557448535628</v>
       </c>
       <c r="C110" t="n">
-        <v>43.8025189346974</v>
+        <v>43.8025188799345</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.0418983192461717</v>
+        <v>-0.0418982843853679</v>
       </c>
     </row>
     <row r="111">
@@ -8757,13 +8757,13 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>773.34089282627</v>
+        <v>773.340892105224</v>
       </c>
       <c r="C111" t="n">
-        <v>46.1092560580363</v>
+        <v>46.1092559993714</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.0289498460666888</v>
+        <v>-0.0289498223946825</v>
       </c>
     </row>
     <row r="112">
@@ -8771,13 +8771,13 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>758.501747870324</v>
+        <v>758.501747193073</v>
       </c>
       <c r="C112" t="n">
-        <v>45.0957115192748</v>
+        <v>45.0957114639305</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.0195179637794327</v>
+        <v>-0.0195179481779882</v>
       </c>
     </row>
     <row r="113">
@@ -8785,13 +8785,13 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>778.19377440895</v>
+        <v>778.193773752982</v>
       </c>
       <c r="C113" t="n">
-        <v>46.4403203947943</v>
+        <v>46.440320340793</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.0136026723844032</v>
+        <v>-0.013602661735285</v>
       </c>
     </row>
     <row r="114">
@@ -8799,13 +8799,13 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>788.252030157257</v>
+        <v>788.252029539459</v>
       </c>
       <c r="C114" t="n">
-        <v>47.127130583454</v>
+        <v>47.1271305319882</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.0112039718816007</v>
+        <v>-0.0112039630665733</v>
       </c>
     </row>
     <row r="115">
@@ -8813,13 +8813,13 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>810.47569694011</v>
+        <v>810.475696317497</v>
       </c>
       <c r="C115" t="n">
-        <v>48.6447021285947</v>
+        <v>48.6447020765935</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.00904710336040286</v>
+        <v>-0.00904709621386554</v>
       </c>
     </row>
     <row r="116">
@@ -8827,13 +8827,13 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>786.053958090725</v>
+        <v>786.053957471255</v>
       </c>
       <c r="C116" t="n">
-        <v>46.9769399801687</v>
+        <v>46.9769399286787</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.00713206682080991</v>
+        <v>-0.00713206117716205</v>
       </c>
     </row>
     <row r="117">
@@ -8841,13 +8841,13 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>819.782733166034</v>
+        <v>819.782732599726</v>
       </c>
       <c r="C117" t="n">
-        <v>49.2801870977099</v>
+        <v>49.2801870495119</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.00545886226282177</v>
+        <v>-0.00545885795646271</v>
       </c>
     </row>
     <row r="118">
@@ -8855,13 +8855,13 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>802.595127915905</v>
+        <v>802.595127250303</v>
       </c>
       <c r="C118" t="n">
-        <v>48.106442604036</v>
+        <v>48.1064425492685</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.0040274896864385</v>
+        <v>-0.00402748655176766</v>
       </c>
     </row>
     <row r="119">
@@ -8869,13 +8869,13 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>840.756826605081</v>
+        <v>840.756826040947</v>
       </c>
       <c r="C119" t="n">
-        <v>50.7124182375083</v>
+        <v>50.7124181892748</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.00288136873234692</v>
+        <v>-0.00288136652920047</v>
       </c>
     </row>
     <row r="120">
@@ -8883,13 +8883,13 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>815.665264695759</v>
+        <v>815.665264129883</v>
       </c>
       <c r="C120" t="n">
-        <v>48.9989377009838</v>
+        <v>48.9989376529182</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.00202049940054703</v>
+        <v>-0.00202049788876115</v>
       </c>
     </row>
     <row r="121">
@@ -8897,13 +8897,13 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>855.306699921817</v>
+        <v>855.306699408136</v>
       </c>
       <c r="C121" t="n">
-        <v>51.7059744430792</v>
+        <v>51.7059743981569</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.00144488169103885</v>
+        <v>-0.00144488063044967</v>
       </c>
     </row>
     <row r="122">
@@ -8911,13 +8911,13 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>830.12510344668</v>
+        <v>830.125102778832</v>
       </c>
       <c r="C122" t="n">
-        <v>49.9863578988554</v>
+        <v>49.9863578436832</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.00115451560382238</v>
+        <v>-0.00115451475426615</v>
       </c>
     </row>
     <row r="123">
@@ -8925,13 +8925,13 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>864.278306115936</v>
+        <v>864.278305568165</v>
       </c>
       <c r="C123" t="n">
-        <v>52.318619181533</v>
+        <v>52.3186191341936</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.000904267790824123</v>
+        <v>-0.000904267124315121</v>
       </c>
     </row>
     <row r="124">
@@ -8939,13 +8939,13 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>847.310521598347</v>
+        <v>847.310521080889</v>
       </c>
       <c r="C124" t="n">
-        <v>51.1599122319014</v>
+        <v>51.1599121868195</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.000694138252044155</v>
+        <v>-0.000694137740596484</v>
       </c>
     </row>
     <row r="125">
@@ -8953,13 +8953,13 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>884.699756167315</v>
+        <v>884.699755668725</v>
       </c>
       <c r="C125" t="n">
-        <v>53.713158602362</v>
+        <v>53.7131585581651</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.000524126987482368</v>
+        <v>-0.000524126603110152</v>
       </c>
     </row>
     <row r="126">
@@ -8967,13 +8967,13 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>870.866039490705</v>
+        <v>870.866038865775</v>
       </c>
       <c r="C126" t="n">
-        <v>52.7684737807251</v>
+        <v>52.768473728053</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.000394233997138818</v>
+        <v>-0.000394233711856283</v>
       </c>
     </row>
     <row r="127">
@@ -8981,13 +8981,13 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>904.645426436074</v>
+        <v>904.645425759357</v>
       </c>
       <c r="C127" t="n">
-        <v>55.0752109040976</v>
+        <v>55.0752108475238</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.000288099683908858</v>
+        <v>-0.000288099478929667</v>
       </c>
     </row>
     <row r="128">
@@ -8995,13 +8995,13 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>889.803328126702</v>
+        <v>889.803327496228</v>
       </c>
       <c r="C128" t="n">
-        <v>54.0616663652848</v>
+        <v>54.0616663120314</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.000205724047792619</v>
+        <v>-0.000205723904330331</v>
       </c>
     </row>
     <row r="129">
@@ -9009,13 +9009,13 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>909.493504639083</v>
+        <v>909.4935040314</v>
       </c>
       <c r="C129" t="n">
-        <v>55.406275240749</v>
+        <v>55.406275188839</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.000147107088790008</v>
+        <v>-0.000147106988058261</v>
       </c>
     </row>
     <row r="130">
@@ -9023,13 +9023,13 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>919.551013689687</v>
+        <v>919.551013120723</v>
       </c>
       <c r="C130" t="n">
-        <v>56.0930854294423</v>
+        <v>56.0930853800676</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.000112248806901025</v>
+        <v>-0.000112248730113403</v>
       </c>
     </row>
     <row r="131">
@@ -9037,13 +9037,13 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>941.774007413114</v>
+        <v>941.774006839839</v>
       </c>
       <c r="C131" t="n">
-        <v>57.6106569746431</v>
+        <v>57.6106569247331</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.000086105095484288</v>
+        <v>-0.0000861050366547447</v>
       </c>
     </row>
     <row r="132">
@@ -9051,13 +9051,13 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>917.351669140453</v>
+        <v>917.351668570773</v>
       </c>
       <c r="C132" t="n">
-        <v>55.9428948261585</v>
+        <v>55.9428947767594</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.0000686759545397964</v>
+        <v>-0.0000686759076823154</v>
       </c>
     </row>
     <row r="133">
@@ -9065,13 +9065,13 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>951.079918432195</v>
+        <v>951.079917916087</v>
       </c>
       <c r="C133" t="n">
-        <v>58.2461419437655</v>
+        <v>58.2461418976586</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.0000599613840675506</v>
+        <v>-0.0000599613431961007</v>
       </c>
     </row>
   </sheetData>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>255.982795813224</v>
+        <v>255.982795813169</v>
       </c>
     </row>
     <row r="3">
@@ -9106,7 +9106,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>261.312073564617</v>
+        <v>261.312073565083</v>
       </c>
     </row>
     <row r="4">
@@ -9114,7 +9114,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>251.389182769784</v>
+        <v>251.389182768018</v>
       </c>
     </row>
     <row r="5">
@@ -9122,7 +9122,7 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>277.172992867541</v>
+        <v>277.172992868896</v>
       </c>
     </row>
     <row r="6">
@@ -9130,7 +9130,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>261.997595884093</v>
+        <v>261.99759589105</v>
       </c>
     </row>
     <row r="7">
@@ -9138,7 +9138,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>266.777352591268</v>
+        <v>266.777352595373</v>
       </c>
     </row>
     <row r="8">
@@ -9146,7 +9146,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>256.253508495529</v>
+        <v>256.253508492043</v>
       </c>
     </row>
     <row r="9">
@@ -9154,7 +9154,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>282.250119866688</v>
+        <v>282.250119859112</v>
       </c>
     </row>
     <row r="10">
@@ -9162,7 +9162,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>268.283503175323</v>
+        <v>268.283503179471</v>
       </c>
     </row>
     <row r="11">
@@ -9170,7 +9170,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>270.32648136992</v>
+        <v>270.326481369067</v>
       </c>
     </row>
     <row r="12">
@@ -9178,7 +9178,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>237.819162619841</v>
+        <v>237.819162613695</v>
       </c>
     </row>
     <row r="13">
@@ -9186,7 +9186,7 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>262.440619972926</v>
+        <v>262.440619975776</v>
       </c>
     </row>
     <row r="14">
@@ -9194,7 +9194,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>240.042920815036</v>
+        <v>240.042920763081</v>
       </c>
     </row>
     <row r="15">
@@ -9202,7 +9202,7 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>228.203929921215</v>
+        <v>228.203929893296</v>
       </c>
     </row>
     <row r="16">
@@ -9210,7 +9210,7 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>207.564875063179</v>
+        <v>207.564875073531</v>
       </c>
     </row>
     <row r="17">
@@ -9218,7 +9218,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>220.027414307894</v>
+        <v>220.027414377415</v>
       </c>
     </row>
     <row r="18">
@@ -9226,7 +9226,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>216.399251709625</v>
+        <v>216.399251627495</v>
       </c>
     </row>
     <row r="19">
@@ -9234,7 +9234,7 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>215.005687479662</v>
+        <v>215.005687459056</v>
       </c>
     </row>
     <row r="20">
@@ -9242,7 +9242,7 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>201.796990968055</v>
+        <v>201.796990996016</v>
       </c>
     </row>
     <row r="21">
@@ -9250,7 +9250,7 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>247.21739258822</v>
+        <v>247.217392662996</v>
       </c>
     </row>
     <row r="22">
@@ -9258,7 +9258,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>228.833487201618</v>
+        <v>228.833487175413</v>
       </c>
     </row>
     <row r="23">
@@ -9266,7 +9266,7 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>222.985308223356</v>
+        <v>222.985308218301</v>
       </c>
     </row>
     <row r="24">
@@ -9274,7 +9274,7 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>206.943153695471</v>
+        <v>206.94315370351</v>
       </c>
     </row>
     <row r="25">
@@ -9282,7 +9282,7 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>244.492601117224</v>
+        <v>244.492601140446</v>
       </c>
     </row>
     <row r="26">
@@ -9290,7 +9290,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>235.960206159004</v>
+        <v>235.960206156979</v>
       </c>
     </row>
     <row r="27">
@@ -9298,7 +9298,7 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>205.959297258621</v>
+        <v>205.959297254804</v>
       </c>
     </row>
     <row r="28">
@@ -9306,7 +9306,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>204.503840137178</v>
+        <v>204.503840136311</v>
       </c>
     </row>
     <row r="29">
@@ -9314,7 +9314,7 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>230.871974264513</v>
+        <v>230.871974271224</v>
       </c>
     </row>
     <row r="30">
@@ -9322,7 +9322,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>257.524477931073</v>
+        <v>257.524477958973</v>
       </c>
     </row>
     <row r="31">
@@ -9330,7 +9330,7 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>246.737105927901</v>
+        <v>246.737105945096</v>
       </c>
     </row>
     <row r="32">
@@ -9338,7 +9338,7 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>224.469613637607</v>
+        <v>224.469613629695</v>
       </c>
     </row>
     <row r="33">
@@ -9346,7 +9346,7 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>255.09342047595</v>
+        <v>255.093420438765</v>
       </c>
     </row>
     <row r="34">
@@ -9354,7 +9354,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>253.725725333807</v>
+        <v>253.725725396531</v>
       </c>
     </row>
     <row r="35">
@@ -9362,7 +9362,7 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>258.11537461217</v>
+        <v>258.115374631454</v>
       </c>
     </row>
     <row r="36">
@@ -9370,7 +9370,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>260.768276989571</v>
+        <v>260.768276967719</v>
       </c>
     </row>
     <row r="37">
@@ -9378,7 +9378,7 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>264.994579151152</v>
+        <v>264.994579090995</v>
       </c>
     </row>
     <row r="38">
@@ -9386,7 +9386,7 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>267.377896311235</v>
+        <v>267.377896328095</v>
       </c>
     </row>
     <row r="39">
@@ -9394,7 +9394,7 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>276.150262285289</v>
+        <v>276.150262281898</v>
       </c>
     </row>
     <row r="40">
@@ -9402,7 +9402,7 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>250.502228078443</v>
+        <v>250.502228064076</v>
       </c>
     </row>
     <row r="41">
@@ -9410,7 +9410,7 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>297.11026728378</v>
+        <v>297.110267284679</v>
       </c>
     </row>
     <row r="42">
@@ -9418,7 +9418,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>267.848933641568</v>
+        <v>267.848933621099</v>
       </c>
     </row>
     <row r="43">
@@ -9426,7 +9426,7 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>277.772921036527</v>
+        <v>277.772921033725</v>
       </c>
     </row>
     <row r="44">
@@ -9434,7 +9434,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>264.82905543948</v>
+        <v>264.829055444194</v>
       </c>
     </row>
     <row r="45">
@@ -9442,7 +9442,7 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>332.63700750994</v>
+        <v>332.637007528499</v>
       </c>
     </row>
     <row r="46">
@@ -9450,7 +9450,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>263.346385599537</v>
+        <v>263.346385557722</v>
       </c>
     </row>
     <row r="47">
@@ -9458,7 +9458,7 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>283.954241065729</v>
+        <v>283.954241041558</v>
       </c>
     </row>
     <row r="48">
@@ -9466,7 +9466,7 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>261.424102537725</v>
+        <v>261.424102542157</v>
       </c>
     </row>
     <row r="49">
@@ -9474,7 +9474,7 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>306.184249099894</v>
+        <v>306.18424916145</v>
       </c>
     </row>
     <row r="50">
@@ -9482,7 +9482,7 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>273.346214898814</v>
+        <v>273.346214862</v>
       </c>
     </row>
     <row r="51">
@@ -9490,7 +9490,7 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>332.745041336489</v>
+        <v>332.745041348223</v>
       </c>
     </row>
     <row r="52">
@@ -9498,7 +9498,7 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>293.483731661643</v>
+        <v>293.48373167751</v>
       </c>
     </row>
     <row r="53">
@@ -9506,7 +9506,7 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>367.019261470462</v>
+        <v>367.019261479676</v>
       </c>
     </row>
     <row r="54">
@@ -9514,7 +9514,7 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>369.272800482928</v>
+        <v>369.272800609177</v>
       </c>
     </row>
     <row r="55">
@@ -9522,7 +9522,7 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>406.483215218855</v>
+        <v>406.48321528131</v>
       </c>
     </row>
     <row r="56">
@@ -9530,7 +9530,7 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>358.500851078175</v>
+        <v>358.500851040648</v>
       </c>
     </row>
     <row r="57">
@@ -9538,7 +9538,7 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>366.923795034997</v>
+        <v>366.92379488382</v>
       </c>
     </row>
     <row r="58">
@@ -9546,7 +9546,7 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>129.656037155289</v>
+        <v>129.656037191797</v>
       </c>
     </row>
     <row r="59">
@@ -9554,7 +9554,7 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>317.253237612197</v>
+        <v>317.253237599077</v>
       </c>
     </row>
     <row r="60">
@@ -9562,7 +9562,7 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>348.969500973955</v>
+        <v>348.969500944586</v>
       </c>
     </row>
     <row r="61">
@@ -9570,7 +9570,7 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>339.381695383643</v>
+        <v>339.381695389626</v>
       </c>
     </row>
     <row r="62">
@@ -9578,7 +9578,7 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>318.814114980929</v>
+        <v>318.814114804645</v>
       </c>
     </row>
     <row r="63">
@@ -9586,7 +9586,7 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>330.992639338383</v>
+        <v>330.992639271651</v>
       </c>
     </row>
     <row r="64">
@@ -9594,7 +9594,7 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>344.407915658947</v>
+        <v>344.407915714534</v>
       </c>
     </row>
     <row r="65">
@@ -9602,7 +9602,7 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>338.655670631493</v>
+        <v>338.655670818923</v>
       </c>
     </row>
     <row r="66">
@@ -9610,7 +9610,7 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>342.987325054088</v>
+        <v>342.987325008007</v>
       </c>
     </row>
     <row r="67">
@@ -9618,7 +9618,7 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>397.289955469336</v>
+        <v>397.289955505723</v>
       </c>
     </row>
     <row r="68">
@@ -9626,7 +9626,7 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>385.30111753914</v>
+        <v>385.301117575954</v>
       </c>
     </row>
     <row r="69">
@@ -9634,7 +9634,7 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>418.178375611118</v>
+        <v>418.178375583999</v>
       </c>
     </row>
     <row r="70">
@@ -9642,7 +9642,7 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>379.900935686686</v>
+        <v>379.900935778683</v>
       </c>
     </row>
     <row r="71">
@@ -9650,7 +9650,7 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>439.586918222457</v>
+        <v>439.586918228478</v>
       </c>
     </row>
     <row r="72">
@@ -9658,7 +9658,7 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>397.143830654391</v>
+        <v>397.143830603387</v>
       </c>
     </row>
     <row r="73">
@@ -9666,7 +9666,7 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>454.209786973039</v>
+        <v>454.209786926025</v>
       </c>
     </row>
     <row r="74">
@@ -9674,7 +9674,7 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>458.03170849824</v>
+        <v>458.031708533422</v>
       </c>
     </row>
     <row r="75">
@@ -9682,7 +9682,7 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>525.96496128</v>
+        <v>525.964961325285</v>
       </c>
     </row>
     <row r="76">
@@ -9690,7 +9690,7 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>487.150022638694</v>
+        <v>487.150022636301</v>
       </c>
     </row>
     <row r="77">
@@ -9698,7 +9698,7 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>528.853307583066</v>
+        <v>528.853307504993</v>
       </c>
     </row>
     <row r="78">
@@ -9706,7 +9706,7 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>548.03509629265</v>
+        <v>548.035096403876</v>
       </c>
     </row>
     <row r="79">
@@ -9714,7 +9714,7 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>569.083117899748</v>
+        <v>569.083117922049</v>
       </c>
     </row>
     <row r="80">
@@ -9722,7 +9722,7 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>492.244747792668</v>
+        <v>492.244747741323</v>
       </c>
     </row>
     <row r="81">
@@ -9730,7 +9730,7 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>490.637038014934</v>
+        <v>490.637037932753</v>
       </c>
     </row>
     <row r="82">
@@ -9738,7 +9738,7 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>615.067031857366</v>
+        <v>615.067031735333</v>
       </c>
     </row>
     <row r="83">
@@ -9746,7 +9746,7 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>608.54430367422</v>
+        <v>608.544303601719</v>
       </c>
     </row>
     <row r="84">
@@ -9754,7 +9754,7 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>573.261626143782</v>
+        <v>573.261626166547</v>
       </c>
     </row>
     <row r="85">
@@ -9762,7 +9762,7 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>559.56934601694</v>
+        <v>559.569346188709</v>
       </c>
     </row>
     <row r="86">
@@ -9770,7 +9770,7 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>521.392751980875</v>
+        <v>521.392751940182</v>
       </c>
     </row>
     <row r="87">
@@ -9778,7 +9778,7 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>616.230594531546</v>
+        <v>616.230594600155</v>
       </c>
     </row>
     <row r="88">
@@ -9786,7 +9786,7 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>533.432332013149</v>
+        <v>533.432332055542</v>
       </c>
     </row>
     <row r="89">
@@ -9794,7 +9794,7 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>581.319872246351</v>
+        <v>581.319872176044</v>
       </c>
     </row>
     <row r="90">
@@ -9802,7 +9802,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>558.87983506323</v>
+        <v>558.879835009461</v>
       </c>
     </row>
     <row r="91">
@@ -9810,7 +9810,7 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>634.558142464341</v>
+        <v>634.558142351149</v>
       </c>
     </row>
     <row r="92">
@@ -9818,7 +9818,7 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>567.000224593935</v>
+        <v>567.000224554668</v>
       </c>
     </row>
     <row r="93">
@@ -9826,7 +9826,7 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>596.568647566407</v>
+        <v>596.568647772636</v>
       </c>
     </row>
     <row r="94">
@@ -9834,7 +9834,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>602.456842116123</v>
+        <v>602.456841778014</v>
       </c>
     </row>
     <row r="95">
@@ -9842,7 +9842,7 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>640.516530819441</v>
+        <v>640.516530727942</v>
       </c>
     </row>
     <row r="96">
@@ -9850,7 +9850,7 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>628.527963345869</v>
+        <v>628.527963499545</v>
       </c>
     </row>
     <row r="97">
@@ -9858,7 +9858,7 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>649.644899770156</v>
+        <v>649.644900046089</v>
       </c>
     </row>
     <row r="98">
@@ -9866,7 +9866,7 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>656.659782073545</v>
+        <v>656.659781662923</v>
       </c>
     </row>
     <row r="99">
@@ -9874,7 +9874,7 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>678.89869479132</v>
+        <v>678.898694362334</v>
       </c>
     </row>
     <row r="100">
@@ -9882,7 +9882,7 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>654.508205519239</v>
+        <v>654.508205065739</v>
       </c>
     </row>
     <row r="101">
@@ -9890,7 +9890,7 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>688.284233817555</v>
+        <v>688.284233375457</v>
       </c>
     </row>
     <row r="102">
@@ -9898,7 +9898,7 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>671.159885431994</v>
+        <v>671.15988483473</v>
       </c>
     </row>
     <row r="103">
@@ -9906,7 +9906,7 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>709.370205950205</v>
+        <v>709.3702054116</v>
       </c>
     </row>
     <row r="104">
@@ -9914,7 +9914,7 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>684.312630833177</v>
+        <v>684.312630263071</v>
       </c>
     </row>
     <row r="105">
@@ -9922,7 +9922,7 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>723.973417815487</v>
+        <v>723.973417280874</v>
       </c>
     </row>
     <row r="106">
@@ -9930,7 +9930,7 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>698.796538060153</v>
+        <v>698.796537367731</v>
       </c>
     </row>
     <row r="107">
@@ -9938,7 +9938,7 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>732.954568270457</v>
+        <v>732.954567694286</v>
       </c>
     </row>
     <row r="108">
@@ -9946,7 +9946,7 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>715.991722116477</v>
+        <v>715.991721566619</v>
       </c>
     </row>
     <row r="109">
@@ -9954,7 +9954,7 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>753.386005871008</v>
+        <v>753.386005335841</v>
       </c>
     </row>
     <row r="110">
@@ -9962,7 +9962,7 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>739.55744920148</v>
+        <v>739.557448535628</v>
       </c>
     </row>
     <row r="111">
@@ -9970,7 +9970,7 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>773.34089282627</v>
+        <v>773.340892105224</v>
       </c>
     </row>
     <row r="112">
@@ -9978,7 +9978,7 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>758.501747870324</v>
+        <v>758.501747193073</v>
       </c>
     </row>
     <row r="113">
@@ -9986,7 +9986,7 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>778.19377440895</v>
+        <v>778.193773752982</v>
       </c>
     </row>
     <row r="114">
@@ -9994,7 +9994,7 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>788.252030157257</v>
+        <v>788.252029539459</v>
       </c>
     </row>
     <row r="115">
@@ -10002,7 +10002,7 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>810.47569694011</v>
+        <v>810.475696317497</v>
       </c>
     </row>
     <row r="116">
@@ -10010,7 +10010,7 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>786.053958090725</v>
+        <v>786.053957471255</v>
       </c>
     </row>
     <row r="117">
@@ -10018,7 +10018,7 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>819.782733166034</v>
+        <v>819.782732599726</v>
       </c>
     </row>
     <row r="118">
@@ -10026,7 +10026,7 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>802.595127915905</v>
+        <v>802.595127250303</v>
       </c>
     </row>
     <row r="119">
@@ -10034,7 +10034,7 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>840.756826605081</v>
+        <v>840.756826040947</v>
       </c>
     </row>
     <row r="120">
@@ -10042,7 +10042,7 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>815.665264695759</v>
+        <v>815.665264129883</v>
       </c>
     </row>
     <row r="121">
@@ -10050,7 +10050,7 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>855.306699921817</v>
+        <v>855.306699408136</v>
       </c>
     </row>
     <row r="122">
@@ -10058,7 +10058,7 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>830.12510344668</v>
+        <v>830.125102778832</v>
       </c>
     </row>
     <row r="123">
@@ -10066,7 +10066,7 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>864.278306115936</v>
+        <v>864.278305568165</v>
       </c>
     </row>
     <row r="124">
@@ -10074,7 +10074,7 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>847.310521598347</v>
+        <v>847.310521080889</v>
       </c>
     </row>
     <row r="125">
@@ -10082,7 +10082,7 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>884.699756167315</v>
+        <v>884.699755668725</v>
       </c>
     </row>
     <row r="126">
@@ -10090,7 +10090,7 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>870.866039490705</v>
+        <v>870.866038865775</v>
       </c>
     </row>
     <row r="127">
@@ -10098,7 +10098,7 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>904.645426436074</v>
+        <v>904.645425759357</v>
       </c>
     </row>
     <row r="128">
@@ -10106,7 +10106,7 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>889.803328126702</v>
+        <v>889.803327496228</v>
       </c>
     </row>
     <row r="129">
@@ -10114,7 +10114,7 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>909.493504639083</v>
+        <v>909.4935040314</v>
       </c>
     </row>
     <row r="130">
@@ -10122,7 +10122,7 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>919.551013689687</v>
+        <v>919.551013120723</v>
       </c>
     </row>
     <row r="131">
@@ -10130,7 +10130,7 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>941.774007413114</v>
+        <v>941.774006839839</v>
       </c>
     </row>
     <row r="132">
@@ -10138,7 +10138,7 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>917.351669140453</v>
+        <v>917.351668570773</v>
       </c>
     </row>
     <row r="133">
@@ -10146,7 +10146,7 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>951.079918432195</v>
+        <v>951.079917916087</v>
       </c>
     </row>
   </sheetData>
